--- a/data/睿博士.xlsx
+++ b/data/睿博士.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4728" uniqueCount="994">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4746" uniqueCount="999">
   <si>
     <t>页面名称</t>
   </si>
@@ -2721,6 +2721,27 @@
     <t>com.zwcode.p6slite:id/obs_wv</t>
   </si>
   <si>
+    <t>事件录像</t>
+  </si>
+  <si>
+    <t>云服务购买协议</t>
+  </si>
+  <si>
+    <t>微信</t>
+  </si>
+  <si>
+    <t>支付宝</t>
+  </si>
+  <si>
+    <t>开通即同意</t>
+  </si>
+  <si>
+    <t>未开通</t>
+  </si>
+  <si>
+    <t>云端存储</t>
+  </si>
+  <si>
     <t>className</t>
   </si>
   <si>
@@ -2997,16 +3018,10 @@
     <t>双目-单通道111</t>
   </si>
   <si>
-    <t>支付宝</t>
-  </si>
-  <si>
     <t>微信购买连续录像</t>
   </si>
   <si>
     <t>双目-双通道22</t>
-  </si>
-  <si>
-    <t>微信</t>
   </si>
   <si>
     <t>打开通知栏</t>
@@ -3026,7 +3041,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3058,6 +3073,12 @@
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF334155"/>
+      <name val="Arial"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -3550,16 +3571,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3568,119 +3586,122 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -3705,6 +3726,7 @@
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -4051,7 +4073,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I923"/>
+  <dimension ref="A1:I932"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.875" customWidth="1"/>
@@ -5589,7 +5611,7 @@
         <v>152</v>
       </c>
       <c r="H107">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="108" spans="1:8">
@@ -5614,7 +5636,7 @@
         <v>155</v>
       </c>
       <c r="H109">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="110" spans="1:8">
@@ -5625,7 +5647,7 @@
         <v>156</v>
       </c>
       <c r="H110">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="111" spans="1:8">
@@ -5675,7 +5697,7 @@
         <v>162</v>
       </c>
       <c r="H114">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115" spans="1:8">
@@ -5700,7 +5722,7 @@
         <v>165</v>
       </c>
       <c r="H116">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="117" spans="1:8">
@@ -5868,7 +5890,7 @@
         <v>185</v>
       </c>
       <c r="H128">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="129" spans="1:8">
@@ -5893,7 +5915,7 @@
         <v>188</v>
       </c>
       <c r="H130">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="131" spans="1:8">
@@ -5907,7 +5929,7 @@
         <v>189</v>
       </c>
       <c r="H131">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="132" spans="1:8">
@@ -5946,7 +5968,7 @@
         <v>192</v>
       </c>
       <c r="H134">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="135" spans="1:8">
@@ -6083,7 +6105,7 @@
         <v>188</v>
       </c>
       <c r="H144">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="145" spans="1:8">
@@ -6094,7 +6116,7 @@
         <v>202</v>
       </c>
       <c r="H145">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="146" spans="1:8">
@@ -6130,7 +6152,7 @@
         <v>206</v>
       </c>
       <c r="H148">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="149" spans="1:8">
@@ -6422,7 +6444,7 @@
         <v>189</v>
       </c>
       <c r="H171">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="172" spans="1:8">
@@ -6433,7 +6455,7 @@
         <v>238</v>
       </c>
       <c r="H172">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="173" spans="1:8">
@@ -6447,7 +6469,7 @@
         <v>240</v>
       </c>
       <c r="H173">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="174" spans="1:8">
@@ -6458,7 +6480,7 @@
         <v>217</v>
       </c>
       <c r="H174">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="175" spans="1:8">
@@ -6525,7 +6547,7 @@
         <v>190</v>
       </c>
       <c r="H179">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="180" spans="1:8">
@@ -6536,7 +6558,7 @@
         <v>246</v>
       </c>
       <c r="H180">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="181" spans="1:8">
@@ -6547,7 +6569,7 @@
         <v>247</v>
       </c>
       <c r="H181">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="182" spans="1:8">
@@ -6572,7 +6594,7 @@
         <v>250</v>
       </c>
       <c r="H183">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="184" spans="1:8">
@@ -6628,7 +6650,7 @@
         <v>192</v>
       </c>
       <c r="H187">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="188" spans="1:8">
@@ -6642,7 +6664,7 @@
         <v>255</v>
       </c>
       <c r="H188">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="189" spans="1:8">
@@ -6656,7 +6678,7 @@
         <v>257</v>
       </c>
       <c r="H189">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="190" spans="1:8">
@@ -6670,7 +6692,7 @@
         <v>258</v>
       </c>
       <c r="H190">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="191" spans="1:8">
@@ -6684,7 +6706,7 @@
         <v>260</v>
       </c>
       <c r="H191">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="192" spans="1:8">
@@ -6698,7 +6720,7 @@
         <v>261</v>
       </c>
       <c r="H192">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="193" spans="1:8">
@@ -6712,7 +6734,7 @@
         <v>262</v>
       </c>
       <c r="H193">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="194" spans="1:8">
@@ -6726,7 +6748,7 @@
         <v>263</v>
       </c>
       <c r="H194">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="195" spans="1:8">
@@ -6740,7 +6762,7 @@
         <v>264</v>
       </c>
       <c r="H195">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="196" spans="1:8">
@@ -6754,7 +6776,7 @@
         <v>265</v>
       </c>
       <c r="H196">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="197" spans="1:8">
@@ -6782,7 +6804,7 @@
         <v>193</v>
       </c>
       <c r="H198">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="199" spans="1:8">
@@ -6807,7 +6829,7 @@
         <v>266</v>
       </c>
       <c r="H200">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="201" spans="1:8">
@@ -6835,7 +6857,7 @@
         <v>194</v>
       </c>
       <c r="H202">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="203" spans="1:8">
@@ -6846,7 +6868,7 @@
         <v>267</v>
       </c>
       <c r="H203">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="204" spans="1:8">
@@ -6874,7 +6896,7 @@
         <v>269</v>
       </c>
       <c r="H205">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="206" spans="1:8">
@@ -7014,7 +7036,7 @@
         <v>195</v>
       </c>
       <c r="H215">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="216" spans="1:8">
@@ -7025,7 +7047,7 @@
         <v>280</v>
       </c>
       <c r="H216">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="217" spans="1:8">
@@ -7050,7 +7072,7 @@
         <v>283</v>
       </c>
       <c r="H218">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="219" spans="1:8">
@@ -7064,7 +7086,7 @@
         <v>285</v>
       </c>
       <c r="H219">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="220" spans="1:8">
@@ -7139,7 +7161,7 @@
         <v>290</v>
       </c>
       <c r="H225">
-        <v>20</v>
+        <v>50</v>
       </c>
     </row>
     <row r="226" spans="1:8">
@@ -7307,7 +7329,7 @@
         <v>200</v>
       </c>
       <c r="H237">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="238" spans="1:8">
@@ -7321,7 +7343,7 @@
         <v>302</v>
       </c>
       <c r="H238">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="239" spans="1:8">
@@ -7335,7 +7357,7 @@
         <v>303</v>
       </c>
       <c r="H239">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="240" spans="1:8">
@@ -7349,7 +7371,7 @@
         <v>304</v>
       </c>
       <c r="H240">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="241" spans="1:8">
@@ -7363,7 +7385,7 @@
         <v>305</v>
       </c>
       <c r="H241">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="242" spans="1:8">
@@ -7564,7 +7586,7 @@
         <v>326</v>
       </c>
       <c r="H256">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="257" spans="1:8">
@@ -7578,7 +7600,7 @@
         <v>328</v>
       </c>
       <c r="H257">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="258" spans="1:8">
@@ -7592,7 +7614,7 @@
         <v>15</v>
       </c>
       <c r="H258">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="259" spans="1:8">
@@ -7603,7 +7625,7 @@
         <v>330</v>
       </c>
       <c r="H259">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="260" spans="1:8">
@@ -7628,7 +7650,7 @@
         <v>333</v>
       </c>
       <c r="H261">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="262" spans="1:8">
@@ -7740,7 +7762,7 @@
         <v>347</v>
       </c>
       <c r="H269">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="270" spans="1:8">
@@ -7751,7 +7773,7 @@
         <v>348</v>
       </c>
       <c r="H270">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="271" spans="1:8">
@@ -7762,7 +7784,7 @@
         <v>349</v>
       </c>
       <c r="H271">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="272" spans="1:8">
@@ -7773,7 +7795,7 @@
         <v>350</v>
       </c>
       <c r="H272">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="273" spans="1:8">
@@ -7784,7 +7806,7 @@
         <v>351</v>
       </c>
       <c r="H273">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="274" spans="1:8">
@@ -7798,7 +7820,7 @@
         <v>353</v>
       </c>
       <c r="H274">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="275" spans="1:8">
@@ -7854,7 +7876,7 @@
         <v>356</v>
       </c>
       <c r="H278">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="279" spans="1:8">
@@ -7868,7 +7890,7 @@
         <v>21</v>
       </c>
       <c r="H279">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="280" spans="1:8">
@@ -7879,7 +7901,7 @@
         <v>317</v>
       </c>
       <c r="H280">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="281" spans="1:8">
@@ -7890,7 +7912,7 @@
         <v>359</v>
       </c>
       <c r="H281">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="282" spans="1:8">
@@ -7901,7 +7923,7 @@
         <v>360</v>
       </c>
       <c r="H282">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="283" spans="1:8">
@@ -7962,7 +7984,7 @@
         <v>366</v>
       </c>
       <c r="H287">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="288" spans="1:8">
@@ -7976,7 +7998,7 @@
         <v>368</v>
       </c>
       <c r="H288">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="289" spans="1:8">
@@ -8123,7 +8145,7 @@
         <v>374</v>
       </c>
       <c r="H300">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="301" spans="1:8">
@@ -8134,7 +8156,7 @@
         <v>375</v>
       </c>
       <c r="H301">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="302" spans="1:8">
@@ -8145,7 +8167,7 @@
         <v>64</v>
       </c>
       <c r="H302">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="303" spans="1:8">
@@ -19619,7 +19641,7 @@
         <v>23</v>
       </c>
       <c r="H892" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I892" s="11" t="s">
         <v>23</v>
@@ -19648,7 +19670,7 @@
         <v>23</v>
       </c>
       <c r="H893" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I893" s="11" t="s">
         <v>23</v>
@@ -19677,7 +19699,7 @@
         <v>23</v>
       </c>
       <c r="H894" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I894" s="11" t="s">
         <v>23</v>
@@ -19706,7 +19728,7 @@
         <v>23</v>
       </c>
       <c r="H895" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I895" s="11" t="s">
         <v>23</v>
@@ -19735,7 +19757,7 @@
         <v>23</v>
       </c>
       <c r="H896" s="11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I896" s="11" t="s">
         <v>23</v>
@@ -19764,7 +19786,7 @@
         <v>23</v>
       </c>
       <c r="H897" s="11">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="I897" s="11" t="s">
         <v>23</v>
@@ -19793,7 +19815,7 @@
         <v>23</v>
       </c>
       <c r="H898" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I898" s="11" t="s">
         <v>23</v>
@@ -19822,7 +19844,7 @@
         <v>23</v>
       </c>
       <c r="H899" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I899" s="11" t="s">
         <v>23</v>
@@ -19851,7 +19873,7 @@
         <v>23</v>
       </c>
       <c r="H900" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I900" s="11" t="s">
         <v>23</v>
@@ -19880,7 +19902,7 @@
         <v>23</v>
       </c>
       <c r="H901" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I901" s="11" t="s">
         <v>23</v>
@@ -19909,7 +19931,7 @@
         <v>23</v>
       </c>
       <c r="H902" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I902" s="11" t="s">
         <v>23</v>
@@ -19938,7 +19960,7 @@
         <v>23</v>
       </c>
       <c r="H903" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I903" s="11" t="s">
         <v>23</v>
@@ -19967,7 +19989,7 @@
         <v>23</v>
       </c>
       <c r="H904" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I904" s="11" t="s">
         <v>23</v>
@@ -19996,7 +20018,7 @@
         <v>23</v>
       </c>
       <c r="H905" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I905" s="11" t="s">
         <v>23</v>
@@ -20025,7 +20047,7 @@
         <v>23</v>
       </c>
       <c r="H906" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I906" s="11" t="s">
         <v>23</v>
@@ -20054,7 +20076,7 @@
         <v>23</v>
       </c>
       <c r="H907" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I907" s="11" t="s">
         <v>23</v>
@@ -20083,7 +20105,7 @@
         <v>23</v>
       </c>
       <c r="H908" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I908" s="11" t="s">
         <v>23</v>
@@ -20112,7 +20134,7 @@
         <v>23</v>
       </c>
       <c r="H909" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I909" s="11" t="s">
         <v>23</v>
@@ -20141,7 +20163,7 @@
         <v>23</v>
       </c>
       <c r="H910" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I910" s="11" t="s">
         <v>23</v>
@@ -20170,7 +20192,7 @@
         <v>23</v>
       </c>
       <c r="H911" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I911" s="11" t="s">
         <v>23</v>
@@ -20199,7 +20221,7 @@
         <v>23</v>
       </c>
       <c r="H912" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I912" s="11" t="s">
         <v>23</v>
@@ -20228,7 +20250,7 @@
         <v>23</v>
       </c>
       <c r="H913" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I913" s="11" t="s">
         <v>23</v>
@@ -20257,7 +20279,7 @@
         <v>23</v>
       </c>
       <c r="H914" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I914" s="11" t="s">
         <v>23</v>
@@ -20286,7 +20308,7 @@
         <v>23</v>
       </c>
       <c r="H915" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I915" s="11" t="s">
         <v>23</v>
@@ -20315,7 +20337,7 @@
         <v>23</v>
       </c>
       <c r="H916" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I916" s="11" t="s">
         <v>23</v>
@@ -20344,7 +20366,7 @@
         <v>23</v>
       </c>
       <c r="H917" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I917" s="11" t="s">
         <v>23</v>
@@ -20373,7 +20395,7 @@
         <v>23</v>
       </c>
       <c r="H918" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I918" s="11" t="s">
         <v>23</v>
@@ -20402,7 +20424,7 @@
         <v>23</v>
       </c>
       <c r="H919" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I919" s="11" t="s">
         <v>23</v>
@@ -20431,7 +20453,7 @@
         <v>23</v>
       </c>
       <c r="H920" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I920" s="11" t="s">
         <v>23</v>
@@ -20460,7 +20482,7 @@
         <v>23</v>
       </c>
       <c r="H921" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I921" s="11" t="s">
         <v>23</v>
@@ -20489,7 +20511,7 @@
         <v>23</v>
       </c>
       <c r="H922" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I922" s="11" t="s">
         <v>23</v>
@@ -20518,10 +20540,109 @@
         <v>23</v>
       </c>
       <c r="H923" s="11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I923" s="11" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="924" ht="15" spans="1:8">
+      <c r="A924" s="11" t="s">
+        <v>883</v>
+      </c>
+      <c r="E924" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="H924">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="925" ht="15" spans="1:8">
+      <c r="A925" s="11" t="s">
+        <v>883</v>
+      </c>
+      <c r="E925" s="12" t="s">
+        <v>896</v>
+      </c>
+      <c r="H925">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="926" ht="15" spans="1:8">
+      <c r="A926" s="11" t="s">
+        <v>883</v>
+      </c>
+      <c r="E926" s="12" t="s">
+        <v>302</v>
+      </c>
+      <c r="H926">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="927" ht="15" spans="1:8">
+      <c r="A927" s="11" t="s">
+        <v>883</v>
+      </c>
+      <c r="E927" s="12" t="s">
+        <v>897</v>
+      </c>
+      <c r="H927">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="928" ht="15" spans="1:8">
+      <c r="A928" s="11" t="s">
+        <v>883</v>
+      </c>
+      <c r="E928" s="12" t="s">
+        <v>898</v>
+      </c>
+      <c r="H928">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="929" ht="15" spans="1:8">
+      <c r="A929" s="11" t="s">
+        <v>883</v>
+      </c>
+      <c r="E929" s="12" t="s">
+        <v>899</v>
+      </c>
+      <c r="H929">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="930" ht="15" spans="1:8">
+      <c r="A930" s="11" t="s">
+        <v>883</v>
+      </c>
+      <c r="E930" s="12" t="s">
+        <v>900</v>
+      </c>
+      <c r="H930">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="931" ht="15" spans="1:8">
+      <c r="A931" s="11" t="s">
+        <v>883</v>
+      </c>
+      <c r="E931" s="12" t="s">
+        <v>901</v>
+      </c>
+      <c r="H931">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="932" ht="15" spans="1:8">
+      <c r="A932" s="11" t="s">
+        <v>883</v>
+      </c>
+      <c r="E932" s="12" t="s">
+        <v>902</v>
+      </c>
+      <c r="H932">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -20557,7 +20678,7 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>896</v>
+        <v>903</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>4</v>
@@ -20583,10 +20704,10 @@
         <v>424</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>897</v>
+        <v>904</v>
       </c>
       <c r="F2" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H2">
         <v>1</v>
@@ -20606,7 +20727,7 @@
         <v>35</v>
       </c>
       <c r="F3" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H3">
         <v>1</v>
@@ -20620,10 +20741,10 @@
         <v>356</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>899</v>
+        <v>906</v>
       </c>
       <c r="F4" t="s">
-        <v>900</v>
+        <v>907</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -20637,10 +20758,10 @@
         <v>185</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>901</v>
+        <v>908</v>
       </c>
       <c r="F5" t="s">
-        <v>900</v>
+        <v>907</v>
       </c>
       <c r="H5">
         <v>1</v>
@@ -20654,13 +20775,13 @@
         <v>22</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>902</v>
+        <v>909</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>22</v>
       </c>
       <c r="F6" t="s">
-        <v>900</v>
+        <v>907</v>
       </c>
       <c r="H6">
         <v>1</v>
@@ -20671,14 +20792,14 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>903</v>
+        <v>910</v>
       </c>
       <c r="C7" s="2"/>
       <c r="E7" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>900</v>
+        <v>907</v>
       </c>
       <c r="H7">
         <v>1</v>
@@ -20692,11 +20813,11 @@
         <v>702</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>904</v>
+        <v>911</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H8">
         <v>1</v>
@@ -20714,7 +20835,7 @@
         <v>20</v>
       </c>
       <c r="F9" t="s">
-        <v>900</v>
+        <v>907</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -20734,7 +20855,7 @@
         <v>407</v>
       </c>
       <c r="F10" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H10">
         <v>1</v>
@@ -20751,7 +20872,7 @@
         <v>665</v>
       </c>
       <c r="F11" t="s">
-        <v>905</v>
+        <v>912</v>
       </c>
       <c r="H11">
         <v>1</v>
@@ -20768,7 +20889,7 @@
         <v>673</v>
       </c>
       <c r="F12" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H12">
         <v>1</v>
@@ -20785,7 +20906,7 @@
         <v>673</v>
       </c>
       <c r="F13" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H13">
         <v>1</v>
@@ -20805,7 +20926,7 @@
         <v>113</v>
       </c>
       <c r="F14" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H14">
         <v>1</v>
@@ -20823,7 +20944,7 @@
         <v>699</v>
       </c>
       <c r="F15" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H15">
         <v>1</v>
@@ -20837,13 +20958,13 @@
         <v>634</v>
       </c>
       <c r="B16" t="s">
-        <v>906</v>
+        <v>913</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>907</v>
+        <v>914</v>
       </c>
       <c r="F16" t="s">
-        <v>905</v>
+        <v>912</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -20854,13 +20975,13 @@
         <v>634</v>
       </c>
       <c r="B17" t="s">
-        <v>906</v>
+        <v>913</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>908</v>
+        <v>915</v>
       </c>
       <c r="F17" t="s">
-        <v>905</v>
+        <v>912</v>
       </c>
       <c r="H17">
         <v>1</v>
@@ -20871,13 +20992,13 @@
         <v>634</v>
       </c>
       <c r="B18" t="s">
-        <v>906</v>
+        <v>913</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>909</v>
+        <v>916</v>
       </c>
       <c r="F18" t="s">
-        <v>905</v>
+        <v>912</v>
       </c>
       <c r="H18">
         <v>1</v>
@@ -20888,13 +21009,13 @@
         <v>634</v>
       </c>
       <c r="B19" t="s">
-        <v>906</v>
+        <v>913</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>910</v>
+        <v>917</v>
       </c>
       <c r="F19" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H19">
         <v>1</v>
@@ -20908,10 +21029,10 @@
         <v>57</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>911</v>
+        <v>918</v>
       </c>
       <c r="F20" t="s">
-        <v>912</v>
+        <v>919</v>
       </c>
       <c r="H20">
         <v>1</v>
@@ -20928,7 +21049,7 @@
         <v>212</v>
       </c>
       <c r="F21" t="s">
-        <v>913</v>
+        <v>920</v>
       </c>
       <c r="H21">
         <v>1</v>
@@ -20948,7 +21069,7 @@
         <v>32</v>
       </c>
       <c r="F22" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H22">
         <v>1</v>
@@ -20964,7 +21085,7 @@
       <c r="C23" s="5"/>
       <c r="E23" s="5"/>
       <c r="F23" t="s">
-        <v>914</v>
+        <v>921</v>
       </c>
       <c r="H23">
         <v>1</v>
@@ -20982,7 +21103,7 @@
         <v>64</v>
       </c>
       <c r="F24" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -20993,14 +21114,14 @@
         <v>561</v>
       </c>
       <c r="B25" t="s">
-        <v>915</v>
+        <v>922</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>588</v>
       </c>
       <c r="E25" s="7"/>
       <c r="F25" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H25">
         <v>1</v>
@@ -21020,7 +21141,7 @@
         <v>62</v>
       </c>
       <c r="F26" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H26">
         <v>1</v>
@@ -21035,10 +21156,10 @@
         <v>9</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>916</v>
+        <v>923</v>
       </c>
       <c r="F27" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H27">
         <v>1</v>
@@ -21049,11 +21170,11 @@
         <v>512</v>
       </c>
       <c r="B28" t="s">
-        <v>917</v>
+        <v>924</v>
       </c>
       <c r="C28" s="2"/>
       <c r="F28" t="s">
-        <v>918</v>
+        <v>925</v>
       </c>
       <c r="G28">
         <v>180</v>
@@ -21076,7 +21197,7 @@
         <v>70</v>
       </c>
       <c r="F29" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H29">
         <v>1</v>
@@ -21096,7 +21217,7 @@
         <v>72</v>
       </c>
       <c r="F30" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H30">
         <v>1</v>
@@ -21113,7 +21234,7 @@
         <v>154</v>
       </c>
       <c r="F31" t="s">
-        <v>905</v>
+        <v>912</v>
       </c>
       <c r="H31">
         <v>1</v>
@@ -21133,7 +21254,7 @@
         <v>165</v>
       </c>
       <c r="F32" t="s">
-        <v>905</v>
+        <v>912</v>
       </c>
       <c r="H32">
         <v>1</v>
@@ -21153,7 +21274,7 @@
         <v>183</v>
       </c>
       <c r="F33" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H33">
         <v>1</v>
@@ -21176,7 +21297,7 @@
         <v>93</v>
       </c>
       <c r="F34" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H34">
         <v>1</v>
@@ -21193,7 +21314,7 @@
         <v>486</v>
       </c>
       <c r="F35" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H35">
         <v>1</v>
@@ -21210,7 +21331,7 @@
         <v>486</v>
       </c>
       <c r="F36" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H36">
         <v>1</v>
@@ -21230,7 +21351,7 @@
         <v>102</v>
       </c>
       <c r="F37" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H37">
         <v>1</v>
@@ -21247,7 +21368,7 @@
         <v>486</v>
       </c>
       <c r="F38" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H38">
         <v>1</v>
@@ -21261,13 +21382,13 @@
         <v>110</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>919</v>
+        <v>926</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>110</v>
       </c>
       <c r="F39" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H39">
         <v>1</v>
@@ -21285,7 +21406,7 @@
         <v>113</v>
       </c>
       <c r="F40" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H40">
         <v>1</v>
@@ -21299,13 +21420,13 @@
         <v>106</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>920</v>
+        <v>927</v>
       </c>
       <c r="E41" s="3" t="s">
         <v>106</v>
       </c>
       <c r="F41" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H41">
         <v>1</v>
@@ -21323,7 +21444,7 @@
         <v>113</v>
       </c>
       <c r="F42" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H42">
         <v>1</v>
@@ -21338,7 +21459,7 @@
       </c>
       <c r="C43" s="2"/>
       <c r="F43" t="s">
-        <v>914</v>
+        <v>921</v>
       </c>
       <c r="H43">
         <v>1</v>
@@ -21354,7 +21475,7 @@
       <c r="C44" s="2"/>
       <c r="E44" s="2"/>
       <c r="F44" t="s">
-        <v>914</v>
+        <v>921</v>
       </c>
       <c r="H44">
         <v>1</v>
@@ -21365,13 +21486,13 @@
         <v>114</v>
       </c>
       <c r="B45" t="s">
-        <v>921</v>
+        <v>928</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>120</v>
       </c>
       <c r="F45" t="s">
-        <v>905</v>
+        <v>912</v>
       </c>
       <c r="G45" s="2"/>
       <c r="H45">
@@ -21383,13 +21504,13 @@
         <v>114</v>
       </c>
       <c r="B46" t="s">
-        <v>921</v>
+        <v>928</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>125</v>
       </c>
       <c r="F46" t="s">
-        <v>905</v>
+        <v>912</v>
       </c>
       <c r="H46">
         <v>1</v>
@@ -21400,7 +21521,7 @@
         <v>114</v>
       </c>
       <c r="B47" t="s">
-        <v>921</v>
+        <v>928</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>128</v>
@@ -21409,7 +21530,7 @@
         <v>113</v>
       </c>
       <c r="F47" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H47">
         <v>1</v>
@@ -21420,7 +21541,7 @@
         <v>114</v>
       </c>
       <c r="B48" t="s">
-        <v>922</v>
+        <v>929</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>122</v>
@@ -21429,7 +21550,7 @@
         <v>123</v>
       </c>
       <c r="F48" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H48">
         <v>1</v>
@@ -21440,13 +21561,13 @@
         <v>114</v>
       </c>
       <c r="B49" t="s">
-        <v>922</v>
+        <v>929</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>573</v>
       </c>
       <c r="F49" t="s">
-        <v>913</v>
+        <v>920</v>
       </c>
       <c r="H49">
         <v>1</v>
@@ -21460,14 +21581,14 @@
         <v>114</v>
       </c>
       <c r="B50" t="s">
-        <v>922</v>
+        <v>929</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s">
-        <v>923</v>
+        <v>930</v>
       </c>
       <c r="F50" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H50">
         <v>1</v>
@@ -21475,14 +21596,14 @@
     </row>
     <row r="51" spans="1:8">
       <c r="A51" t="s">
-        <v>921</v>
+        <v>928</v>
       </c>
       <c r="B51" t="s">
         <v>133</v>
       </c>
       <c r="C51" s="2"/>
       <c r="F51" t="s">
-        <v>914</v>
+        <v>921</v>
       </c>
       <c r="H51">
         <v>1</v>
@@ -21490,14 +21611,14 @@
     </row>
     <row r="52" spans="1:8">
       <c r="A52" t="s">
-        <v>921</v>
+        <v>928</v>
       </c>
       <c r="B52" t="s">
-        <v>924</v>
+        <v>931</v>
       </c>
       <c r="C52" s="2"/>
       <c r="F52" t="s">
-        <v>914</v>
+        <v>921</v>
       </c>
       <c r="H52">
         <v>1</v>
@@ -21505,14 +21626,14 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" t="s">
-        <v>921</v>
+        <v>928</v>
       </c>
       <c r="B53" t="s">
-        <v>925</v>
+        <v>932</v>
       </c>
       <c r="C53" s="2"/>
       <c r="F53" t="s">
-        <v>914</v>
+        <v>921</v>
       </c>
       <c r="H53">
         <v>1</v>
@@ -21520,19 +21641,19 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" t="s">
-        <v>925</v>
+        <v>932</v>
       </c>
       <c r="B54" t="s">
         <v>591</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>926</v>
+        <v>933</v>
       </c>
       <c r="E54" t="s">
-        <v>927</v>
+        <v>934</v>
       </c>
       <c r="F54" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H54">
         <v>1</v>
@@ -21540,19 +21661,19 @@
     </row>
     <row r="55" customFormat="1" spans="1:8">
       <c r="A55" t="s">
-        <v>925</v>
+        <v>932</v>
       </c>
       <c r="B55" t="s">
         <v>591</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>928</v>
+        <v>935</v>
       </c>
       <c r="E55" t="s">
         <v>344</v>
       </c>
       <c r="F55" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H55">
         <v>1</v>
@@ -21569,7 +21690,7 @@
         <v>573</v>
       </c>
       <c r="F56" t="s">
-        <v>929</v>
+        <v>936</v>
       </c>
       <c r="H56">
         <v>1</v>
@@ -21587,10 +21708,10 @@
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s">
-        <v>923</v>
+        <v>930</v>
       </c>
       <c r="F57" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H57">
         <v>1</v>
@@ -21610,7 +21731,7 @@
         <v>573</v>
       </c>
       <c r="F58" t="s">
-        <v>929</v>
+        <v>936</v>
       </c>
       <c r="H58">
         <v>1</v>
@@ -21618,14 +21739,14 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" t="s">
-        <v>924</v>
+        <v>931</v>
       </c>
       <c r="B59" t="s">
         <v>138</v>
       </c>
       <c r="C59" s="2"/>
       <c r="F59" t="s">
-        <v>914</v>
+        <v>921</v>
       </c>
       <c r="H59">
         <v>1</v>
@@ -21633,14 +21754,14 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" t="s">
-        <v>930</v>
+        <v>937</v>
       </c>
       <c r="B60" t="s">
         <v>138</v>
       </c>
       <c r="C60" s="2"/>
       <c r="F60" t="s">
-        <v>914</v>
+        <v>921</v>
       </c>
       <c r="H60">
         <v>1</v>
@@ -21651,7 +21772,7 @@
         <v>133</v>
       </c>
       <c r="B61" t="s">
-        <v>930</v>
+        <v>937</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>128</v>
@@ -21660,7 +21781,7 @@
         <v>136</v>
       </c>
       <c r="F61" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H61">
         <v>1</v>
@@ -21671,7 +21792,7 @@
         <v>138</v>
       </c>
       <c r="B62" t="s">
-        <v>917</v>
+        <v>924</v>
       </c>
       <c r="C62" t="s">
         <v>66</v>
@@ -21680,7 +21801,7 @@
         <v>138</v>
       </c>
       <c r="F62" t="s">
-        <v>918</v>
+        <v>925</v>
       </c>
       <c r="G62">
         <v>180</v>
@@ -21691,13 +21812,13 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63" t="s">
-        <v>917</v>
+        <v>924</v>
       </c>
       <c r="B63" t="s">
         <v>433</v>
       </c>
       <c r="F63" t="s">
-        <v>914</v>
+        <v>921</v>
       </c>
       <c r="H63">
         <v>1</v>
@@ -21705,13 +21826,13 @@
     </row>
     <row r="64" customFormat="1" spans="1:8">
       <c r="A64" t="s">
-        <v>917</v>
+        <v>924</v>
       </c>
       <c r="B64" t="s">
         <v>143</v>
       </c>
       <c r="F64" t="s">
-        <v>914</v>
+        <v>921</v>
       </c>
       <c r="H64">
         <v>1</v>
@@ -21731,7 +21852,7 @@
         <v>446</v>
       </c>
       <c r="F65" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H65">
         <v>1</v>
@@ -21776,19 +21897,19 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68" t="s">
-        <v>925</v>
+        <v>932</v>
       </c>
       <c r="B68" t="s">
-        <v>931</v>
+        <v>938</v>
       </c>
       <c r="C68" t="s">
-        <v>926</v>
+        <v>933</v>
       </c>
       <c r="E68" t="s">
-        <v>927</v>
+        <v>934</v>
       </c>
       <c r="F68" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H68">
         <v>1</v>
@@ -21796,19 +21917,19 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69" t="s">
-        <v>925</v>
+        <v>932</v>
       </c>
       <c r="B69" t="s">
-        <v>931</v>
+        <v>938</v>
       </c>
       <c r="C69" t="s">
-        <v>928</v>
+        <v>935</v>
       </c>
       <c r="E69" t="s">
         <v>344</v>
       </c>
       <c r="F69" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H69">
         <v>1</v>
@@ -21826,7 +21947,7 @@
         <v>188</v>
       </c>
       <c r="F70" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H70">
         <v>1</v>
@@ -21843,7 +21964,7 @@
         <v>189</v>
       </c>
       <c r="F71" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H71">
         <v>1</v>
@@ -21860,7 +21981,7 @@
         <v>190</v>
       </c>
       <c r="F72" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H72">
         <v>1</v>
@@ -21877,7 +21998,7 @@
         <v>192</v>
       </c>
       <c r="F73" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H73">
         <v>1</v>
@@ -21894,7 +22015,7 @@
         <v>193</v>
       </c>
       <c r="F74" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H74">
         <v>1</v>
@@ -21911,7 +22032,7 @@
         <v>194</v>
       </c>
       <c r="F75" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H75">
         <v>1</v>
@@ -21928,7 +22049,7 @@
         <v>195</v>
       </c>
       <c r="F76" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H76">
         <v>1</v>
@@ -21945,7 +22066,7 @@
         <v>198</v>
       </c>
       <c r="F77" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H77">
         <v>1</v>
@@ -21962,7 +22083,7 @@
         <v>19</v>
       </c>
       <c r="F78" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H78">
         <v>1</v>
@@ -21979,7 +22100,7 @@
         <v>200</v>
       </c>
       <c r="F79" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H79">
         <v>1</v>
@@ -21996,7 +22117,7 @@
         <v>326</v>
       </c>
       <c r="F80" t="s">
-        <v>900</v>
+        <v>907</v>
       </c>
       <c r="H80">
         <v>1</v>
@@ -22007,13 +22128,13 @@
         <v>185</v>
       </c>
       <c r="B81" t="s">
-        <v>932</v>
+        <v>939</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>932</v>
+        <v>939</v>
       </c>
       <c r="F81" t="s">
-        <v>900</v>
+        <v>907</v>
       </c>
       <c r="H81">
         <v>1</v>
@@ -22024,13 +22145,13 @@
         <v>185</v>
       </c>
       <c r="B82" t="s">
-        <v>932</v>
+        <v>939</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>933</v>
+        <v>940</v>
       </c>
       <c r="F82" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H82">
         <v>1</v>
@@ -22041,13 +22162,13 @@
         <v>185</v>
       </c>
       <c r="B83" t="s">
-        <v>932</v>
+        <v>939</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>934</v>
+        <v>941</v>
       </c>
       <c r="F83" t="s">
-        <v>918</v>
+        <v>925</v>
       </c>
       <c r="H83">
         <v>1</v>
@@ -22058,13 +22179,13 @@
         <v>185</v>
       </c>
       <c r="B84" t="s">
-        <v>932</v>
+        <v>939</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>935</v>
+        <v>942</v>
       </c>
       <c r="F84" t="s">
-        <v>918</v>
+        <v>925</v>
       </c>
       <c r="H84">
         <v>1</v>
@@ -22078,10 +22199,10 @@
         <v>338</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>936</v>
+        <v>943</v>
       </c>
       <c r="F85" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H85">
         <v>1</v>
@@ -22095,13 +22216,13 @@
         <v>346</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>937</v>
+        <v>944</v>
       </c>
       <c r="E86" s="2" t="s">
         <v>346</v>
       </c>
       <c r="F86" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H86">
         <v>1</v>
@@ -22121,7 +22242,7 @@
         <v>516</v>
       </c>
       <c r="F87" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H87">
         <v>1</v>
@@ -22132,14 +22253,14 @@
         <v>185</v>
       </c>
       <c r="B88" t="s">
-        <v>938</v>
+        <v>945</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>532</v>
       </c>
       <c r="E88" s="3"/>
       <c r="F88" t="s">
-        <v>939</v>
+        <v>946</v>
       </c>
       <c r="H88">
         <v>1</v>
@@ -22153,11 +22274,11 @@
         <v>185</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>940</v>
+        <v>947</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H89">
         <v>1</v>
@@ -22171,10 +22292,10 @@
         <v>185</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>940</v>
+        <v>947</v>
       </c>
       <c r="F90" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H90">
         <v>1</v>
@@ -22188,10 +22309,10 @@
         <v>185</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>940</v>
+        <v>947</v>
       </c>
       <c r="F91" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H91">
         <v>1</v>
@@ -22205,10 +22326,10 @@
         <v>185</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>940</v>
+        <v>947</v>
       </c>
       <c r="F92" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H92">
         <v>1</v>
@@ -22225,7 +22346,7 @@
         <v>486</v>
       </c>
       <c r="F93" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H93">
         <v>1</v>
@@ -22242,7 +22363,7 @@
         <v>486</v>
       </c>
       <c r="F94" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H94">
         <v>1</v>
@@ -22256,10 +22377,10 @@
         <v>185</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>940</v>
+        <v>947</v>
       </c>
       <c r="F95" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H95">
         <v>1</v>
@@ -22276,7 +22397,7 @@
         <v>486</v>
       </c>
       <c r="F96" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H96">
         <v>1</v>
@@ -22293,7 +22414,7 @@
         <v>486</v>
       </c>
       <c r="F97" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H97">
         <v>1</v>
@@ -22310,7 +22431,7 @@
         <v>486</v>
       </c>
       <c r="F98" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H98">
         <v>1</v>
@@ -22324,10 +22445,10 @@
         <v>185</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>940</v>
+        <v>947</v>
       </c>
       <c r="F99" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H99">
         <v>1</v>
@@ -22347,7 +22468,7 @@
         <v>342</v>
       </c>
       <c r="F100" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H100">
         <v>1</v>
@@ -22367,7 +22488,7 @@
         <v>355</v>
       </c>
       <c r="F101" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H101">
         <v>1</v>
@@ -22381,13 +22502,13 @@
         <v>21</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>941</v>
+        <v>948</v>
       </c>
       <c r="E102" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F102" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H102">
         <v>1</v>
@@ -22401,10 +22522,10 @@
         <v>9</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>940</v>
+        <v>947</v>
       </c>
       <c r="F103" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H103">
         <v>1</v>
@@ -22415,13 +22536,13 @@
         <v>356</v>
       </c>
       <c r="B104" t="s">
-        <v>942</v>
+        <v>949</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>943</v>
+        <v>950</v>
       </c>
       <c r="F104" t="s">
-        <v>912</v>
+        <v>919</v>
       </c>
       <c r="H104">
         <v>1</v>
@@ -22432,14 +22553,14 @@
         <v>356</v>
       </c>
       <c r="B105" t="s">
-        <v>942</v>
+        <v>949</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>543</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s">
-        <v>913</v>
+        <v>920</v>
       </c>
       <c r="H105">
         <v>1</v>
@@ -22459,7 +22580,7 @@
         <v>356</v>
       </c>
       <c r="F106" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H106">
         <v>1</v>
@@ -22473,10 +22594,10 @@
         <v>9</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>940</v>
+        <v>947</v>
       </c>
       <c r="F107" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H107">
         <v>1</v>
@@ -22496,7 +22617,7 @@
         <v>366</v>
       </c>
       <c r="F108" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H108">
         <v>1</v>
@@ -22516,7 +22637,7 @@
         <v>368</v>
       </c>
       <c r="F109" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H109">
         <v>1</v>
@@ -22533,7 +22654,7 @@
         <v>9</v>
       </c>
       <c r="F110" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H110">
         <v>1</v>
@@ -22550,7 +22671,7 @@
         <v>380</v>
       </c>
       <c r="F111" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H111">
         <v>1</v>
@@ -22567,7 +22688,7 @@
         <v>64</v>
       </c>
       <c r="F112" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H112">
         <v>1</v>
@@ -22578,14 +22699,14 @@
         <v>64</v>
       </c>
       <c r="B113" t="s">
-        <v>944</v>
+        <v>951</v>
       </c>
       <c r="C113" t="s">
-        <v>945</v>
+        <v>952</v>
       </c>
       <c r="E113" s="3"/>
       <c r="F113" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H113">
         <v>1</v>
@@ -22596,13 +22717,13 @@
         <v>64</v>
       </c>
       <c r="B114" t="s">
-        <v>944</v>
+        <v>951</v>
       </c>
       <c r="E114" s="3" t="s">
         <v>335</v>
       </c>
       <c r="F114" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H114">
         <v>1</v>
@@ -22613,13 +22734,13 @@
         <v>64</v>
       </c>
       <c r="B115" t="s">
-        <v>944</v>
+        <v>951</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>946</v>
+        <v>953</v>
       </c>
       <c r="F115" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H115">
         <v>1</v>
@@ -22633,13 +22754,13 @@
         <v>64</v>
       </c>
       <c r="B116" t="s">
-        <v>944</v>
+        <v>951</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>947</v>
+        <v>954</v>
       </c>
       <c r="F116" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H116">
         <v>1</v>
@@ -22650,13 +22771,13 @@
         <v>64</v>
       </c>
       <c r="B117" t="s">
-        <v>944</v>
+        <v>951</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>948</v>
+        <v>955</v>
       </c>
       <c r="F117" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H117">
         <v>1</v>
@@ -22667,14 +22788,14 @@
         <v>64</v>
       </c>
       <c r="B118" t="s">
-        <v>949</v>
+        <v>956</v>
       </c>
       <c r="C118" t="s">
         <v>780</v>
       </c>
       <c r="E118" s="3"/>
       <c r="F118" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H118">
         <v>1</v>
@@ -22685,13 +22806,13 @@
         <v>64</v>
       </c>
       <c r="B119" t="s">
-        <v>949</v>
+        <v>956</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>950</v>
+        <v>957</v>
       </c>
       <c r="F119" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H119">
         <v>1</v>
@@ -22702,13 +22823,13 @@
         <v>64</v>
       </c>
       <c r="B120" t="s">
-        <v>949</v>
+        <v>956</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>951</v>
+        <v>958</v>
       </c>
       <c r="F120" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H120">
         <v>1</v>
@@ -22719,13 +22840,13 @@
         <v>64</v>
       </c>
       <c r="B121" t="s">
-        <v>949</v>
+        <v>956</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>952</v>
+        <v>959</v>
       </c>
       <c r="F121" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H121">
         <v>1</v>
@@ -22739,10 +22860,10 @@
         <v>35</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>940</v>
+        <v>947</v>
       </c>
       <c r="F122" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H122">
         <v>1</v>
@@ -22759,10 +22880,10 @@
         <v>390</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="F123" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H123">
         <v>1</v>
@@ -22776,13 +22897,13 @@
         <v>392</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>954</v>
+        <v>961</v>
       </c>
       <c r="E124" s="4" t="s">
         <v>344</v>
       </c>
       <c r="F124" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H124">
         <v>1</v>
@@ -22800,7 +22921,7 @@
         <v>389</v>
       </c>
       <c r="F125" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H125">
         <v>1</v>
@@ -22814,13 +22935,13 @@
         <v>389</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>955</v>
+        <v>962</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>956</v>
+        <v>963</v>
       </c>
       <c r="F126" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H126">
         <v>1</v>
@@ -22834,13 +22955,13 @@
         <v>389</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>954</v>
+        <v>961</v>
       </c>
       <c r="E127" s="6" t="s">
         <v>344</v>
       </c>
       <c r="F127" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H127">
         <v>1</v>
@@ -22858,7 +22979,7 @@
         <v>699</v>
       </c>
       <c r="F128" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H128">
         <v>1</v>
@@ -22872,14 +22993,14 @@
         <v>389</v>
       </c>
       <c r="B129" t="s">
-        <v>957</v>
+        <v>964</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>694</v>
       </c>
       <c r="E129" s="6"/>
       <c r="F129" t="s">
-        <v>905</v>
+        <v>912</v>
       </c>
       <c r="H129">
         <v>1</v>
@@ -22890,14 +23011,14 @@
         <v>389</v>
       </c>
       <c r="B130" t="s">
-        <v>957</v>
+        <v>964</v>
       </c>
       <c r="C130" s="2"/>
       <c r="E130" s="7" t="s">
         <v>446</v>
       </c>
       <c r="F130" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H130">
         <v>1</v>
@@ -22915,7 +23036,7 @@
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s">
-        <v>905</v>
+        <v>912</v>
       </c>
       <c r="H131">
         <v>1</v>
@@ -22932,7 +23053,7 @@
         <v>399</v>
       </c>
       <c r="F132" t="s">
-        <v>905</v>
+        <v>912</v>
       </c>
       <c r="H132">
         <v>1</v>
@@ -22946,10 +23067,10 @@
         <v>9</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>958</v>
+        <v>965</v>
       </c>
       <c r="F133" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H133">
         <v>1</v>
@@ -22966,7 +23087,7 @@
         <v>403</v>
       </c>
       <c r="F134" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H134">
         <v>1</v>
@@ -22983,7 +23104,7 @@
         <v>478</v>
       </c>
       <c r="F135" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H135">
         <v>1</v>
@@ -23011,16 +23132,16 @@
         <v>22</v>
       </c>
       <c r="B137" t="s">
-        <v>959</v>
+        <v>966</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>960</v>
+        <v>967</v>
       </c>
       <c r="E137" t="s">
-        <v>959</v>
+        <v>966</v>
       </c>
       <c r="F137" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H137">
         <v>1</v>
@@ -23031,16 +23152,16 @@
         <v>22</v>
       </c>
       <c r="B138" t="s">
-        <v>959</v>
+        <v>966</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>928</v>
+        <v>935</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>344</v>
       </c>
       <c r="F138" t="s">
-        <v>912</v>
+        <v>919</v>
       </c>
       <c r="H138">
         <v>1</v>
@@ -23051,14 +23172,14 @@
         <v>22</v>
       </c>
       <c r="B139" t="s">
-        <v>959</v>
+        <v>966</v>
       </c>
       <c r="C139" s="2"/>
       <c r="E139" s="3" t="s">
         <v>353</v>
       </c>
       <c r="F139" t="s">
-        <v>912</v>
+        <v>919</v>
       </c>
       <c r="H139">
         <v>1</v>
@@ -23109,7 +23230,7 @@
         <v>762</v>
       </c>
       <c r="F142" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H142">
         <v>1</v>
@@ -23126,7 +23247,7 @@
         <v>723</v>
       </c>
       <c r="F143" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H143">
         <v>1</v>
@@ -23140,7 +23261,7 @@
         <v>21</v>
       </c>
       <c r="F144" t="s">
-        <v>914</v>
+        <v>921</v>
       </c>
       <c r="H144">
         <v>1</v>
@@ -23154,10 +23275,10 @@
         <v>21</v>
       </c>
       <c r="C145" t="s">
-        <v>961</v>
+        <v>968</v>
       </c>
       <c r="F145" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H145">
         <v>1</v>
@@ -23185,13 +23306,13 @@
         <v>723</v>
       </c>
       <c r="B147" t="s">
-        <v>962</v>
+        <v>969</v>
       </c>
       <c r="C147" t="s">
         <v>740</v>
       </c>
       <c r="F147" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H147">
         <v>1</v>
@@ -23202,13 +23323,13 @@
         <v>723</v>
       </c>
       <c r="B148" t="s">
-        <v>963</v>
+        <v>970</v>
       </c>
       <c r="C148" t="s">
         <v>734</v>
       </c>
       <c r="F148" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H148">
         <v>1</v>
@@ -23219,10 +23340,10 @@
         <v>723</v>
       </c>
       <c r="B149" t="s">
-        <v>964</v>
+        <v>971</v>
       </c>
       <c r="F149" t="s">
-        <v>964</v>
+        <v>971</v>
       </c>
       <c r="H149">
         <v>1</v>
@@ -23239,7 +23360,7 @@
         <v>744</v>
       </c>
       <c r="F150" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H150">
         <v>1</v>
@@ -23250,10 +23371,10 @@
         <v>866</v>
       </c>
       <c r="B151" t="s">
-        <v>965</v>
+        <v>972</v>
       </c>
       <c r="F151" t="s">
-        <v>965</v>
+        <v>972</v>
       </c>
       <c r="H151">
         <v>1</v>
@@ -23264,10 +23385,10 @@
         <v>866</v>
       </c>
       <c r="B152" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="F152" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="H152">
         <v>1</v>
@@ -23284,7 +23405,7 @@
         <v>344</v>
       </c>
       <c r="F153" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H153">
         <v>1</v>
@@ -23295,13 +23416,13 @@
         <v>516</v>
       </c>
       <c r="B154" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="C154" t="s">
         <v>523</v>
       </c>
       <c r="F154" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H154">
         <v>1</v>
@@ -23312,7 +23433,7 @@
         <v>326</v>
       </c>
       <c r="B155" t="s">
-        <v>968</v>
+        <v>975</v>
       </c>
       <c r="C155" t="s">
         <v>334</v>
@@ -23321,7 +23442,7 @@
         <v>335</v>
       </c>
       <c r="F155" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H155">
         <v>1</v>
@@ -23332,13 +23453,13 @@
         <v>326</v>
       </c>
       <c r="B156" t="s">
-        <v>968</v>
+        <v>975</v>
       </c>
       <c r="E156" t="s">
-        <v>969</v>
+        <v>976</v>
       </c>
       <c r="F156" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H156">
         <v>1</v>
@@ -23349,16 +23470,16 @@
         <v>185</v>
       </c>
       <c r="B157" t="s">
-        <v>970</v>
+        <v>977</v>
       </c>
       <c r="C157" t="s">
         <v>187</v>
       </c>
       <c r="E157" t="s">
-        <v>970</v>
+        <v>977</v>
       </c>
       <c r="F157" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H157">
         <v>1</v>
@@ -23369,13 +23490,13 @@
         <v>185</v>
       </c>
       <c r="B158" t="s">
-        <v>970</v>
+        <v>977</v>
       </c>
       <c r="E158" t="s">
-        <v>933</v>
+        <v>940</v>
       </c>
       <c r="F158" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H158">
         <v>1</v>
@@ -23386,13 +23507,13 @@
         <v>185</v>
       </c>
       <c r="B159" t="s">
-        <v>970</v>
+        <v>977</v>
       </c>
       <c r="E159" t="s">
-        <v>971</v>
+        <v>978</v>
       </c>
       <c r="F159" t="s">
-        <v>918</v>
+        <v>925</v>
       </c>
       <c r="H159">
         <v>1</v>
@@ -23403,13 +23524,13 @@
         <v>326</v>
       </c>
       <c r="B160" t="s">
-        <v>972</v>
+        <v>979</v>
       </c>
       <c r="E160" t="s">
         <v>337</v>
       </c>
       <c r="F160" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H160">
         <v>1</v>
@@ -23420,13 +23541,13 @@
         <v>326</v>
       </c>
       <c r="B161" t="s">
-        <v>972</v>
+        <v>979</v>
       </c>
       <c r="C161" t="s">
-        <v>973</v>
+        <v>980</v>
       </c>
       <c r="F161" t="s">
-        <v>905</v>
+        <v>912</v>
       </c>
       <c r="H161">
         <v>1</v>
@@ -23437,13 +23558,13 @@
         <v>326</v>
       </c>
       <c r="B162" t="s">
-        <v>972</v>
+        <v>979</v>
       </c>
       <c r="E162" t="s">
-        <v>974</v>
+        <v>981</v>
       </c>
       <c r="F162" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H162">
         <v>1</v>
@@ -23454,13 +23575,13 @@
         <v>326</v>
       </c>
       <c r="B163" t="s">
-        <v>972</v>
+        <v>979</v>
       </c>
       <c r="E163" t="s">
-        <v>951</v>
+        <v>958</v>
       </c>
       <c r="F163" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H163">
         <v>1</v>
@@ -23477,7 +23598,7 @@
         <v>712</v>
       </c>
       <c r="F164" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H164">
         <v>1</v>
@@ -23494,7 +23615,7 @@
         <v>709</v>
       </c>
       <c r="F165" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H165">
         <v>1</v>
@@ -23505,13 +23626,13 @@
         <v>712</v>
       </c>
       <c r="B166" t="s">
-        <v>975</v>
+        <v>982</v>
       </c>
       <c r="C166" t="s">
         <v>327</v>
       </c>
       <c r="F166" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H166">
         <v>1</v>
@@ -23522,13 +23643,13 @@
         <v>712</v>
       </c>
       <c r="B167" t="s">
-        <v>975</v>
+        <v>982</v>
       </c>
       <c r="E167" t="s">
-        <v>975</v>
+        <v>982</v>
       </c>
       <c r="F167" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H167">
         <v>1</v>
@@ -23539,13 +23660,13 @@
         <v>326</v>
       </c>
       <c r="B168" t="s">
-        <v>976</v>
+        <v>983</v>
       </c>
       <c r="C168" t="s">
         <v>334</v>
       </c>
       <c r="F168" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H168">
         <v>1</v>
@@ -23556,13 +23677,13 @@
         <v>326</v>
       </c>
       <c r="B169" t="s">
-        <v>976</v>
+        <v>983</v>
       </c>
       <c r="C169" t="s">
-        <v>973</v>
+        <v>980</v>
       </c>
       <c r="F169" t="s">
-        <v>905</v>
+        <v>912</v>
       </c>
       <c r="H169">
         <v>1</v>
@@ -23573,13 +23694,13 @@
         <v>326</v>
       </c>
       <c r="B170" t="s">
-        <v>976</v>
+        <v>983</v>
       </c>
       <c r="C170" t="s">
         <v>334</v>
       </c>
       <c r="F170" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H170">
         <v>1</v>
@@ -23590,13 +23711,13 @@
         <v>709</v>
       </c>
       <c r="B171" t="s">
-        <v>977</v>
+        <v>984</v>
       </c>
       <c r="C171" t="s">
-        <v>978</v>
+        <v>985</v>
       </c>
       <c r="F171" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H171">
         <v>1</v>
@@ -23607,13 +23728,13 @@
         <v>709</v>
       </c>
       <c r="B172" t="s">
-        <v>977</v>
+        <v>984</v>
       </c>
       <c r="C172" t="s">
-        <v>979</v>
+        <v>986</v>
       </c>
       <c r="F172" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H172">
         <v>1</v>
@@ -23624,13 +23745,13 @@
         <v>326</v>
       </c>
       <c r="B173" t="s">
-        <v>969</v>
+        <v>976</v>
       </c>
       <c r="E173" t="s">
         <v>335</v>
       </c>
       <c r="F173" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H173">
         <v>1</v>
@@ -23641,13 +23762,13 @@
         <v>326</v>
       </c>
       <c r="B174" t="s">
-        <v>969</v>
+        <v>976</v>
       </c>
       <c r="E174" t="s">
-        <v>969</v>
+        <v>976</v>
       </c>
       <c r="F174" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H174">
         <v>1</v>
@@ -23658,7 +23779,7 @@
         <v>326</v>
       </c>
       <c r="B175" t="s">
-        <v>969</v>
+        <v>976</v>
       </c>
       <c r="F175" t="s">
         <v>361</v>
@@ -23672,13 +23793,13 @@
         <v>326</v>
       </c>
       <c r="B176" t="s">
-        <v>980</v>
+        <v>987</v>
       </c>
       <c r="E176" t="s">
         <v>335</v>
       </c>
       <c r="F176" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H176">
         <v>1</v>
@@ -23689,13 +23810,13 @@
         <v>326</v>
       </c>
       <c r="B177" t="s">
-        <v>980</v>
+        <v>987</v>
       </c>
       <c r="E177" t="s">
-        <v>980</v>
+        <v>987</v>
       </c>
       <c r="F177" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H177">
         <v>1</v>
@@ -23709,13 +23830,13 @@
         <v>326</v>
       </c>
       <c r="B178" t="s">
-        <v>980</v>
+        <v>987</v>
       </c>
       <c r="E178" t="s">
-        <v>947</v>
+        <v>954</v>
       </c>
       <c r="F178" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H178">
         <v>1</v>
@@ -23726,13 +23847,13 @@
         <v>326</v>
       </c>
       <c r="B179" t="s">
-        <v>980</v>
+        <v>987</v>
       </c>
       <c r="E179" t="s">
         <v>335</v>
       </c>
       <c r="F179" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H179">
         <v>1</v>
@@ -23743,13 +23864,13 @@
         <v>326</v>
       </c>
       <c r="B180" t="s">
-        <v>980</v>
+        <v>987</v>
       </c>
       <c r="E180" t="s">
-        <v>981</v>
+        <v>988</v>
       </c>
       <c r="F180" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H180">
         <v>1</v>
@@ -23760,13 +23881,13 @@
         <v>326</v>
       </c>
       <c r="B181" t="s">
-        <v>980</v>
+        <v>987</v>
       </c>
       <c r="E181" t="s">
-        <v>947</v>
+        <v>954</v>
       </c>
       <c r="F181" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H181">
         <v>1</v>
@@ -23777,13 +23898,13 @@
         <v>290</v>
       </c>
       <c r="B182" t="s">
-        <v>982</v>
+        <v>989</v>
       </c>
       <c r="C182" t="s">
         <v>523</v>
       </c>
       <c r="F182" t="s">
-        <v>983</v>
+        <v>990</v>
       </c>
       <c r="H182">
         <v>1</v>
@@ -23800,7 +23921,7 @@
         <v>883</v>
       </c>
       <c r="F183" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H183">
         <v>1</v>
@@ -23814,13 +23935,13 @@
         <v>290</v>
       </c>
       <c r="B184" t="s">
-        <v>984</v>
+        <v>991</v>
       </c>
       <c r="E184" t="s">
-        <v>985</v>
+        <v>992</v>
       </c>
       <c r="F184" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H184">
         <v>1</v>
@@ -23831,13 +23952,13 @@
         <v>290</v>
       </c>
       <c r="B185" t="s">
-        <v>984</v>
+        <v>991</v>
       </c>
       <c r="E185" t="s">
         <v>299</v>
       </c>
       <c r="F185" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H185">
         <v>1</v>
@@ -23845,13 +23966,13 @@
     </row>
     <row r="186" spans="1:8">
       <c r="A186" t="s">
-        <v>984</v>
+        <v>991</v>
       </c>
       <c r="B186" t="s">
         <v>883</v>
       </c>
       <c r="F186" t="s">
-        <v>914</v>
+        <v>921</v>
       </c>
       <c r="H186">
         <v>1</v>
@@ -23862,13 +23983,13 @@
         <v>883</v>
       </c>
       <c r="B187" t="s">
-        <v>986</v>
+        <v>993</v>
       </c>
       <c r="E187" t="s">
         <v>302</v>
       </c>
       <c r="F187" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H187">
         <v>1</v>
@@ -23879,13 +24000,13 @@
         <v>883</v>
       </c>
       <c r="B188" t="s">
-        <v>986</v>
+        <v>993</v>
       </c>
       <c r="E188" s="9" t="s">
-        <v>987</v>
+        <v>994</v>
       </c>
       <c r="F188" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H188">
         <v>1</v>
@@ -23896,13 +24017,13 @@
         <v>883</v>
       </c>
       <c r="B189" t="s">
-        <v>986</v>
+        <v>993</v>
       </c>
       <c r="E189" t="s">
-        <v>988</v>
+        <v>899</v>
       </c>
       <c r="F189" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H189">
         <v>1</v>
@@ -23913,13 +24034,13 @@
         <v>883</v>
       </c>
       <c r="B190" t="s">
-        <v>989</v>
+        <v>995</v>
       </c>
       <c r="E190" t="s">
         <v>302</v>
       </c>
       <c r="F190" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H190">
         <v>1</v>
@@ -23930,13 +24051,13 @@
         <v>883</v>
       </c>
       <c r="B191" t="s">
-        <v>989</v>
+        <v>995</v>
       </c>
       <c r="E191" s="9" t="s">
-        <v>990</v>
+        <v>996</v>
       </c>
       <c r="F191" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H191">
         <v>1</v>
@@ -23947,13 +24068,13 @@
         <v>883</v>
       </c>
       <c r="B192" t="s">
-        <v>989</v>
+        <v>995</v>
       </c>
       <c r="E192" t="s">
-        <v>991</v>
+        <v>898</v>
       </c>
       <c r="F192" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="H192">
         <v>1</v>
@@ -23970,7 +24091,7 @@
         <v>842</v>
       </c>
       <c r="F193" t="s">
-        <v>992</v>
+        <v>997</v>
       </c>
       <c r="H193">
         <v>1</v>
@@ -23981,10 +24102,10 @@
         <v>809</v>
       </c>
       <c r="B194" t="s">
-        <v>993</v>
+        <v>998</v>
       </c>
       <c r="F194" t="s">
-        <v>993</v>
+        <v>998</v>
       </c>
       <c r="H194">
         <v>1</v>

--- a/data/睿博士.xlsx
+++ b/data/睿博士.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4754" uniqueCount="999">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4842" uniqueCount="1019">
   <si>
     <t>页面名称</t>
   </si>
@@ -2766,9 +2766,33 @@
     <t>云消息</t>
   </si>
   <si>
+    <t>布撤防</t>
+  </si>
+  <si>
+    <t>立即开启</t>
+  </si>
+  <si>
+    <t>非必选按钮</t>
+  </si>
+  <si>
+    <t>确认</t>
+  </si>
+  <si>
     <t>com.zwcode.p6slite:id/tv_share_messages</t>
   </si>
   <si>
+    <t>删除全部云消息</t>
+  </si>
+  <si>
+    <t>com.zwcode.p6slite:id/iv_edit</t>
+  </si>
+  <si>
+    <t>com.zwcode.p6slite:id/tv_select_all</t>
+  </si>
+  <si>
+    <t>com.zwcode.p6slite:id/frag_alarm_select_delete</t>
+  </si>
+  <si>
     <t>文本框</t>
   </si>
   <si>
@@ -2790,9 +2814,6 @@
     <t>com.zwcode.p6slite:id/popup_close_btn</t>
   </si>
   <si>
-    <t>非必选按钮</t>
-  </si>
-  <si>
     <t>可变文本</t>
   </si>
   <si>
@@ -2928,6 +2949,9 @@
     <t>完成注销</t>
   </si>
   <si>
+    <t>选择国家</t>
+  </si>
+  <si>
     <t>com.zwcode.p6slite:id/read_privacy_check_box</t>
   </si>
   <si>
@@ -3028,6 +3052,42 @@
   </si>
   <si>
     <t>关闭通知栏</t>
+  </si>
+  <si>
+    <t>移动侦测开关</t>
+  </si>
+  <si>
+    <t>开关</t>
+  </si>
+  <si>
+    <t>人形侦测开关</t>
+  </si>
+  <si>
+    <t>设置灵敏度</t>
+  </si>
+  <si>
+    <t>com.zwcode.p6slite:id/segment_view</t>
+  </si>
+  <si>
+    <t>灵敏度</t>
+  </si>
+  <si>
+    <t>清除设置区域</t>
+  </si>
+  <si>
+    <t>com.zwcode.p6slite:id/layout_monitor_area_aiot</t>
+  </si>
+  <si>
+    <t>选择区域</t>
+  </si>
+  <si>
+    <t>保存设置区域</t>
+  </si>
+  <si>
+    <t>com.zwcode.p6slite:id/frag_dev_osd_name</t>
+  </si>
+  <si>
+    <t>OSD使能开关</t>
   </si>
 </sst>
 </file>
@@ -20647,7 +20707,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J196"/>
+  <dimension ref="A1:J218"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="14.875" customWidth="1"/>
@@ -20802,32 +20862,32 @@
         <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>702</v>
-      </c>
-      <c r="C8" s="2" t="s">
         <v>911</v>
       </c>
-      <c r="E8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="E8" s="3" t="s">
+        <v>912</v>
+      </c>
       <c r="F8" t="s">
-        <v>905</v>
+        <v>913</v>
       </c>
       <c r="H8">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" customFormat="1" spans="1:8">
       <c r="A9" t="s">
         <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>911</v>
       </c>
       <c r="C9" s="2"/>
-      <c r="E9" s="2" t="s">
-        <v>20</v>
+      <c r="E9" s="3" t="s">
+        <v>914</v>
       </c>
       <c r="F9" t="s">
-        <v>907</v>
+        <v>913</v>
       </c>
       <c r="H9">
         <v>1</v>
@@ -20835,17 +20895,15 @@
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>392</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>634</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>407</v>
-      </c>
+        <v>702</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>915</v>
+      </c>
+      <c r="E10" s="2"/>
       <c r="F10" t="s">
         <v>905</v>
       </c>
@@ -20855,48 +20913,51 @@
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>392</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>634</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>665</v>
+        <v>20</v>
+      </c>
+      <c r="C11" s="2"/>
+      <c r="E11" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="F11" t="s">
-        <v>912</v>
+        <v>907</v>
       </c>
       <c r="H11">
         <v>1</v>
       </c>
     </row>
-    <row r="12" customFormat="1" spans="1:8">
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>392</v>
+        <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>634</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>673</v>
+        <v>916</v>
+      </c>
+      <c r="C12" s="2"/>
+      <c r="E12" s="2" t="s">
+        <v>16</v>
       </c>
       <c r="F12" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="H12">
         <v>1</v>
       </c>
     </row>
-    <row r="13" customFormat="1" spans="1:8">
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>392</v>
+        <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>634</v>
+        <v>916</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>673</v>
-      </c>
+        <v>917</v>
+      </c>
+      <c r="E13" s="2"/>
       <c r="F13" t="s">
         <v>905</v>
       </c>
@@ -20904,19 +20965,17 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" customFormat="1" spans="1:8">
       <c r="A14" t="s">
-        <v>392</v>
+        <v>9</v>
       </c>
       <c r="B14" t="s">
-        <v>634</v>
+        <v>916</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>679</v>
-      </c>
-      <c r="E14" t="s">
-        <v>113</v>
-      </c>
+        <v>918</v>
+      </c>
+      <c r="E14" s="2"/>
       <c r="F14" t="s">
         <v>905</v>
       </c>
@@ -20924,39 +20983,37 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" customFormat="1" spans="1:8">
       <c r="A15" t="s">
-        <v>634</v>
+        <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>699</v>
-      </c>
-      <c r="C15" s="2"/>
-      <c r="E15" t="s">
-        <v>699</v>
-      </c>
+        <v>916</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>919</v>
+      </c>
+      <c r="E15" s="2"/>
       <c r="F15" t="s">
         <v>905</v>
       </c>
       <c r="H15">
         <v>1</v>
       </c>
-      <c r="I15">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
+    </row>
+    <row r="16" customFormat="1" spans="1:8">
       <c r="A16" t="s">
-        <v>634</v>
+        <v>9</v>
       </c>
       <c r="B16" t="s">
-        <v>913</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>914</v>
+        <v>916</v>
+      </c>
+      <c r="C16" s="2"/>
+      <c r="E16" s="3" t="s">
+        <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>912</v>
+        <v>905</v>
       </c>
       <c r="H16">
         <v>1</v>
@@ -20964,16 +21021,19 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" t="s">
+        <v>392</v>
+      </c>
+      <c r="B17" t="s">
         <v>634</v>
       </c>
-      <c r="B17" t="s">
-        <v>913</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>915</v>
+      <c r="C17" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>407</v>
       </c>
       <c r="F17" t="s">
-        <v>912</v>
+        <v>905</v>
       </c>
       <c r="H17">
         <v>1</v>
@@ -20981,30 +21041,30 @@
     </row>
     <row r="18" spans="1:8">
       <c r="A18" t="s">
+        <v>392</v>
+      </c>
+      <c r="B18" t="s">
         <v>634</v>
       </c>
-      <c r="B18" t="s">
-        <v>913</v>
-      </c>
       <c r="C18" s="2" t="s">
-        <v>916</v>
+        <v>665</v>
       </c>
       <c r="F18" t="s">
-        <v>912</v>
+        <v>920</v>
       </c>
       <c r="H18">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" customFormat="1" spans="1:8">
       <c r="A19" t="s">
+        <v>392</v>
+      </c>
+      <c r="B19" t="s">
         <v>634</v>
       </c>
-      <c r="B19" t="s">
-        <v>913</v>
-      </c>
       <c r="C19" s="2" t="s">
-        <v>917</v>
+        <v>673</v>
       </c>
       <c r="F19" t="s">
         <v>905</v>
@@ -21013,52 +21073,53 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" customFormat="1" spans="1:8">
       <c r="A20" t="s">
-        <v>424</v>
+        <v>392</v>
       </c>
       <c r="B20" t="s">
-        <v>57</v>
+        <v>634</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>918</v>
+        <v>673</v>
       </c>
       <c r="F20" t="s">
-        <v>919</v>
+        <v>905</v>
       </c>
       <c r="H20">
         <v>1</v>
       </c>
     </row>
-    <row r="21" ht="14.25" spans="1:8">
+    <row r="21" spans="1:8">
       <c r="A21" t="s">
-        <v>424</v>
+        <v>392</v>
       </c>
       <c r="B21" t="s">
-        <v>114</v>
+        <v>634</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>212</v>
+        <v>679</v>
+      </c>
+      <c r="E21" t="s">
+        <v>113</v>
       </c>
       <c r="F21" t="s">
-        <v>920</v>
+        <v>905</v>
       </c>
       <c r="H21">
         <v>1</v>
       </c>
     </row>
-    <row r="22" ht="14.25" spans="1:8">
+    <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>424</v>
+        <v>634</v>
       </c>
       <c r="B22" t="s">
-        <v>114</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>432</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>32</v>
+        <v>699</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="E22" t="s">
+        <v>699</v>
       </c>
       <c r="F22" t="s">
         <v>905</v>
@@ -21066,18 +21127,22 @@
       <c r="H22">
         <v>1</v>
       </c>
+      <c r="I22">
+        <v>10</v>
+      </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" t="s">
-        <v>424</v>
+        <v>634</v>
       </c>
       <c r="B23" t="s">
-        <v>512</v>
-      </c>
-      <c r="C23" s="5"/>
-      <c r="E23" s="5"/>
+        <v>921</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>922</v>
+      </c>
       <c r="F23" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H23">
         <v>1</v>
@@ -21085,17 +21150,16 @@
     </row>
     <row r="24" spans="1:8">
       <c r="A24" t="s">
-        <v>57</v>
+        <v>634</v>
       </c>
       <c r="B24" t="s">
-        <v>561</v>
-      </c>
-      <c r="C24" s="6"/>
-      <c r="E24" s="7" t="s">
-        <v>64</v>
+        <v>921</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>923</v>
       </c>
       <c r="F24" t="s">
-        <v>905</v>
+        <v>920</v>
       </c>
       <c r="H24">
         <v>1</v>
@@ -21103,34 +21167,30 @@
     </row>
     <row r="25" spans="1:8">
       <c r="A25" t="s">
-        <v>561</v>
+        <v>634</v>
       </c>
       <c r="B25" t="s">
-        <v>922</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>588</v>
-      </c>
-      <c r="E25" s="7"/>
+        <v>921</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>924</v>
+      </c>
       <c r="F25" t="s">
-        <v>905</v>
+        <v>920</v>
       </c>
       <c r="H25">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:8">
       <c r="A26" t="s">
-        <v>57</v>
+        <v>634</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>921</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>62</v>
+        <v>925</v>
       </c>
       <c r="F26" t="s">
         <v>905</v>
@@ -21138,55 +21198,53 @@
       <c r="H26">
         <v>1</v>
       </c>
-      <c r="J26" s="2"/>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" t="s">
+        <v>424</v>
+      </c>
+      <c r="B27" t="s">
         <v>57</v>
       </c>
-      <c r="B27" t="s">
-        <v>9</v>
-      </c>
       <c r="C27" s="2" t="s">
-        <v>923</v>
+        <v>926</v>
       </c>
       <c r="F27" t="s">
-        <v>905</v>
+        <v>913</v>
       </c>
       <c r="H27">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" ht="14.25" spans="1:8">
       <c r="A28" t="s">
-        <v>512</v>
+        <v>424</v>
       </c>
       <c r="B28" t="s">
-        <v>924</v>
-      </c>
-      <c r="C28" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>212</v>
+      </c>
       <c r="F28" t="s">
-        <v>925</v>
-      </c>
-      <c r="G28">
-        <v>180</v>
+        <v>927</v>
       </c>
       <c r="H28">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" ht="14.25" spans="1:8">
       <c r="A29" t="s">
+        <v>424</v>
+      </c>
+      <c r="B29" t="s">
+        <v>114</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="E29" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="B29" t="s">
-        <v>80</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="F29" t="s">
         <v>905</v>
@@ -21197,73 +21255,68 @@
     </row>
     <row r="30" spans="1:8">
       <c r="A30" t="s">
+        <v>424</v>
+      </c>
+      <c r="B30" t="s">
+        <v>512</v>
+      </c>
+      <c r="C30" s="5"/>
+      <c r="E30" s="5"/>
+      <c r="F30" t="s">
+        <v>928</v>
+      </c>
+      <c r="H30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" t="s">
+        <v>57</v>
+      </c>
+      <c r="B31" t="s">
+        <v>561</v>
+      </c>
+      <c r="C31" s="6"/>
+      <c r="E31" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="F31" t="s">
+        <v>905</v>
+      </c>
+      <c r="H31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" t="s">
+        <v>561</v>
+      </c>
+      <c r="B32" t="s">
+        <v>929</v>
+      </c>
+      <c r="C32" s="6" t="s">
+        <v>588</v>
+      </c>
+      <c r="E32" s="7"/>
+      <c r="F32" t="s">
+        <v>905</v>
+      </c>
+      <c r="H32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="A33" t="s">
+        <v>57</v>
+      </c>
+      <c r="B33" t="s">
         <v>32</v>
       </c>
-      <c r="B30" t="s">
-        <v>152</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F30" t="s">
-        <v>905</v>
-      </c>
-      <c r="H30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" customFormat="1" spans="1:8">
-      <c r="A31" t="s">
-        <v>32</v>
-      </c>
-      <c r="B31" t="s">
-        <v>152</v>
-      </c>
-      <c r="C31" t="s">
-        <v>154</v>
-      </c>
-      <c r="F31" t="s">
-        <v>912</v>
-      </c>
-      <c r="H31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" customFormat="1" spans="1:8">
-      <c r="A32" t="s">
-        <v>32</v>
-      </c>
-      <c r="B32" t="s">
-        <v>152</v>
-      </c>
-      <c r="C32" t="s">
-        <v>164</v>
-      </c>
-      <c r="E32" t="s">
-        <v>165</v>
-      </c>
-      <c r="F32" t="s">
-        <v>912</v>
-      </c>
-      <c r="H32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" customFormat="1" spans="1:9">
-      <c r="A33" t="s">
-        <v>32</v>
-      </c>
-      <c r="B33" t="s">
-        <v>152</v>
-      </c>
-      <c r="C33" t="s">
-        <v>182</v>
-      </c>
-      <c r="E33" t="s">
-        <v>183</v>
+      <c r="C33" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="F33" t="s">
         <v>905</v>
@@ -21271,22 +21324,17 @@
       <c r="H33">
         <v>1</v>
       </c>
-      <c r="I33">
-        <v>5</v>
-      </c>
+      <c r="J33" s="2"/>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" t="s">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="B34" t="s">
-        <v>96</v>
+        <v>9</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>93</v>
+        <v>930</v>
       </c>
       <c r="F34" t="s">
         <v>905</v>
@@ -21297,16 +21345,17 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" t="s">
-        <v>80</v>
+        <v>512</v>
       </c>
       <c r="B35" t="s">
-        <v>32</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>486</v>
-      </c>
+        <v>931</v>
+      </c>
+      <c r="C35" s="2"/>
       <c r="F35" t="s">
-        <v>905</v>
+        <v>932</v>
+      </c>
+      <c r="G35">
+        <v>180</v>
       </c>
       <c r="H35">
         <v>1</v>
@@ -21314,13 +21363,16 @@
     </row>
     <row r="36" spans="1:8">
       <c r="A36" t="s">
-        <v>96</v>
+        <v>32</v>
       </c>
       <c r="B36" t="s">
         <v>80</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>486</v>
+        <v>69</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="F36" t="s">
         <v>905</v>
@@ -21331,16 +21383,16 @@
     </row>
     <row r="37" spans="1:8">
       <c r="A37" t="s">
-        <v>96</v>
+        <v>32</v>
       </c>
       <c r="B37" t="s">
-        <v>103</v>
+        <v>152</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>102</v>
+        <v>72</v>
       </c>
       <c r="F37" t="s">
         <v>905</v>
@@ -21349,53 +21401,55 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" customFormat="1" spans="1:8">
       <c r="A38" t="s">
-        <v>103</v>
+        <v>32</v>
       </c>
       <c r="B38" t="s">
-        <v>96</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>486</v>
+        <v>152</v>
+      </c>
+      <c r="C38" t="s">
+        <v>154</v>
       </c>
       <c r="F38" t="s">
-        <v>905</v>
+        <v>920</v>
       </c>
       <c r="H38">
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" customFormat="1" spans="1:8">
       <c r="A39" t="s">
-        <v>103</v>
+        <v>32</v>
       </c>
       <c r="B39" t="s">
-        <v>110</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>926</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>110</v>
+        <v>152</v>
+      </c>
+      <c r="C39" t="s">
+        <v>164</v>
+      </c>
+      <c r="E39" t="s">
+        <v>165</v>
       </c>
       <c r="F39" t="s">
-        <v>905</v>
+        <v>920</v>
       </c>
       <c r="H39">
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" customFormat="1" spans="1:9">
       <c r="A40" t="s">
-        <v>103</v>
+        <v>32</v>
       </c>
       <c r="B40" t="s">
-        <v>110</v>
-      </c>
-      <c r="C40" s="2"/>
-      <c r="E40" s="2" t="s">
-        <v>113</v>
+        <v>152</v>
+      </c>
+      <c r="C40" t="s">
+        <v>182</v>
+      </c>
+      <c r="E40" t="s">
+        <v>183</v>
       </c>
       <c r="F40" t="s">
         <v>905</v>
@@ -21403,19 +21457,22 @@
       <c r="H40">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" customFormat="1" spans="1:8">
+      <c r="I40">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
       <c r="A41" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="B41" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>927</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>106</v>
+        <v>92</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="F41" t="s">
         <v>905</v>
@@ -21424,16 +21481,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" customFormat="1" spans="1:8">
+    <row r="42" spans="1:8">
       <c r="A42" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="B42" t="s">
-        <v>106</v>
-      </c>
-      <c r="C42" s="2"/>
-      <c r="E42" s="2" t="s">
-        <v>113</v>
+        <v>32</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>486</v>
       </c>
       <c r="F42" t="s">
         <v>905</v>
@@ -21444,65 +21500,73 @@
     </row>
     <row r="43" spans="1:8">
       <c r="A43" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="B43" t="s">
-        <v>114</v>
-      </c>
-      <c r="C43" s="2"/>
+        <v>80</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>486</v>
+      </c>
       <c r="F43" t="s">
-        <v>921</v>
+        <v>905</v>
       </c>
       <c r="H43">
         <v>1</v>
       </c>
     </row>
-    <row r="44" ht="14.25" spans="1:8">
+    <row r="44" spans="1:8">
       <c r="A44" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="B44" t="s">
-        <v>114</v>
-      </c>
-      <c r="C44" s="2"/>
-      <c r="E44" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>102</v>
+      </c>
       <c r="F44" t="s">
-        <v>921</v>
+        <v>905</v>
       </c>
       <c r="H44">
         <v>1</v>
       </c>
     </row>
-    <row r="45" ht="14.25" spans="1:8">
+    <row r="45" spans="1:8">
       <c r="A45" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B45" t="s">
-        <v>928</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>120</v>
+        <v>96</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>486</v>
       </c>
       <c r="F45" t="s">
-        <v>912</v>
-      </c>
-      <c r="G45" s="2"/>
+        <v>905</v>
+      </c>
       <c r="H45">
         <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B46" t="s">
-        <v>928</v>
+        <v>110</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>125</v>
+        <v>933</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>110</v>
       </c>
       <c r="F46" t="s">
-        <v>912</v>
+        <v>905</v>
       </c>
       <c r="H46">
         <v>1</v>
@@ -21510,14 +21574,12 @@
     </row>
     <row r="47" spans="1:8">
       <c r="A47" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B47" t="s">
-        <v>928</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>128</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="C47" s="2"/>
       <c r="E47" s="2" t="s">
         <v>113</v>
       </c>
@@ -21528,18 +21590,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" customFormat="1" spans="1:8">
       <c r="A48" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B48" t="s">
-        <v>929</v>
+        <v>106</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>122</v>
+        <v>934</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="F48" t="s">
         <v>905</v>
@@ -21548,84 +21610,85 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:9">
+    <row r="49" customFormat="1" spans="1:8">
       <c r="A49" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="B49" t="s">
-        <v>929</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>573</v>
+        <v>106</v>
+      </c>
+      <c r="C49" s="2"/>
+      <c r="E49" s="2" t="s">
+        <v>113</v>
       </c>
       <c r="F49" t="s">
-        <v>920</v>
+        <v>905</v>
       </c>
       <c r="H49">
         <v>1</v>
-      </c>
-      <c r="I49">
-        <v>10</v>
       </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" t="s">
+        <v>110</v>
+      </c>
+      <c r="B50" t="s">
         <v>114</v>
       </c>
-      <c r="B50" t="s">
-        <v>929</v>
-      </c>
       <c r="C50" s="2"/>
-      <c r="D50" t="s">
-        <v>930</v>
-      </c>
       <c r="F50" t="s">
-        <v>905</v>
+        <v>928</v>
       </c>
       <c r="H50">
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" ht="14.25" spans="1:8">
       <c r="A51" t="s">
+        <v>106</v>
+      </c>
+      <c r="B51" t="s">
+        <v>114</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s">
         <v>928</v>
       </c>
-      <c r="B51" t="s">
-        <v>133</v>
-      </c>
-      <c r="C51" s="2"/>
-      <c r="F51" t="s">
-        <v>921</v>
-      </c>
       <c r="H51">
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" ht="14.25" spans="1:8">
       <c r="A52" t="s">
-        <v>928</v>
+        <v>114</v>
       </c>
       <c r="B52" t="s">
-        <v>931</v>
-      </c>
-      <c r="C52" s="2"/>
+        <v>935</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>120</v>
+      </c>
       <c r="F52" t="s">
-        <v>921</v>
-      </c>
+        <v>920</v>
+      </c>
+      <c r="G52" s="2"/>
       <c r="H52">
         <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" t="s">
-        <v>928</v>
+        <v>114</v>
       </c>
       <c r="B53" t="s">
-        <v>932</v>
-      </c>
-      <c r="C53" s="2"/>
+        <v>935</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>125</v>
+      </c>
       <c r="F53" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="H53">
         <v>1</v>
@@ -21633,16 +21696,16 @@
     </row>
     <row r="54" spans="1:8">
       <c r="A54" t="s">
-        <v>932</v>
+        <v>114</v>
       </c>
       <c r="B54" t="s">
-        <v>591</v>
+        <v>935</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>933</v>
-      </c>
-      <c r="E54" t="s">
-        <v>934</v>
+        <v>128</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>113</v>
       </c>
       <c r="F54" t="s">
         <v>905</v>
@@ -21651,18 +21714,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" customFormat="1" spans="1:8">
+    <row r="55" spans="1:8">
       <c r="A55" t="s">
-        <v>932</v>
+        <v>114</v>
       </c>
       <c r="B55" t="s">
-        <v>591</v>
+        <v>936</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>935</v>
-      </c>
-      <c r="E55" t="s">
-        <v>344</v>
+        <v>122</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>123</v>
       </c>
       <c r="F55" t="s">
         <v>905</v>
@@ -21671,36 +21734,36 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" customFormat="1" spans="1:9">
+    <row r="56" spans="1:9">
       <c r="A56" t="s">
-        <v>591</v>
+        <v>114</v>
       </c>
       <c r="B56" t="s">
-        <v>138</v>
+        <v>936</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>573</v>
       </c>
       <c r="F56" t="s">
+        <v>927</v>
+      </c>
+      <c r="H56">
+        <v>1</v>
+      </c>
+      <c r="I56">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" t="s">
+        <v>114</v>
+      </c>
+      <c r="B57" t="s">
         <v>936</v>
-      </c>
-      <c r="H56">
-        <v>1</v>
-      </c>
-      <c r="I56">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="57" customFormat="1" spans="1:9">
-      <c r="A57" t="s">
-        <v>591</v>
-      </c>
-      <c r="B57" t="s">
-        <v>138</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s">
-        <v>930</v>
+        <v>937</v>
       </c>
       <c r="F57" t="s">
         <v>905</v>
@@ -21708,22 +21771,17 @@
       <c r="H57">
         <v>1</v>
       </c>
-      <c r="I57">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="58" customFormat="1" spans="1:8">
+    </row>
+    <row r="58" spans="1:8">
       <c r="A58" t="s">
-        <v>591</v>
+        <v>935</v>
       </c>
       <c r="B58" t="s">
-        <v>138</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>573</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="C58" s="2"/>
       <c r="F58" t="s">
-        <v>936</v>
+        <v>928</v>
       </c>
       <c r="H58">
         <v>1</v>
@@ -21731,14 +21789,14 @@
     </row>
     <row r="59" spans="1:8">
       <c r="A59" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="B59" t="s">
-        <v>138</v>
+        <v>938</v>
       </c>
       <c r="C59" s="2"/>
       <c r="F59" t="s">
-        <v>921</v>
+        <v>928</v>
       </c>
       <c r="H59">
         <v>1</v>
@@ -21746,14 +21804,14 @@
     </row>
     <row r="60" spans="1:8">
       <c r="A60" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="B60" t="s">
-        <v>138</v>
+        <v>939</v>
       </c>
       <c r="C60" s="2"/>
       <c r="F60" t="s">
-        <v>921</v>
+        <v>928</v>
       </c>
       <c r="H60">
         <v>1</v>
@@ -21761,16 +21819,16 @@
     </row>
     <row r="61" spans="1:8">
       <c r="A61" t="s">
-        <v>133</v>
+        <v>939</v>
       </c>
       <c r="B61" t="s">
-        <v>937</v>
+        <v>591</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>136</v>
+        <v>940</v>
+      </c>
+      <c r="E61" t="s">
+        <v>941</v>
       </c>
       <c r="F61" t="s">
         <v>905</v>
@@ -21779,109 +21837,109 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62" customFormat="1" spans="1:8">
       <c r="A62" t="s">
+        <v>939</v>
+      </c>
+      <c r="B62" t="s">
+        <v>591</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="E62" t="s">
+        <v>344</v>
+      </c>
+      <c r="F62" t="s">
+        <v>905</v>
+      </c>
+      <c r="H62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" customFormat="1" spans="1:9">
+      <c r="A63" t="s">
+        <v>591</v>
+      </c>
+      <c r="B63" t="s">
         <v>138</v>
       </c>
-      <c r="B62" t="s">
-        <v>924</v>
-      </c>
-      <c r="C62" t="s">
-        <v>66</v>
-      </c>
-      <c r="E62" t="s">
+      <c r="C63" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="F63" t="s">
+        <v>943</v>
+      </c>
+      <c r="H63">
+        <v>1</v>
+      </c>
+      <c r="I63">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" customFormat="1" spans="1:9">
+      <c r="A64" t="s">
+        <v>591</v>
+      </c>
+      <c r="B64" t="s">
         <v>138</v>
       </c>
-      <c r="F62" t="s">
-        <v>925</v>
-      </c>
-      <c r="G62">
-        <v>180</v>
-      </c>
-      <c r="H62">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8">
-      <c r="A63" t="s">
-        <v>924</v>
-      </c>
-      <c r="B63" t="s">
-        <v>433</v>
-      </c>
-      <c r="F63" t="s">
-        <v>921</v>
-      </c>
-      <c r="H63">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="64" customFormat="1" spans="1:8">
-      <c r="A64" t="s">
-        <v>924</v>
-      </c>
-      <c r="B64" t="s">
-        <v>143</v>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s">
+        <v>937</v>
       </c>
       <c r="F64" t="s">
-        <v>921</v>
+        <v>905</v>
       </c>
       <c r="H64">
         <v>1</v>
       </c>
-    </row>
-    <row r="65" spans="1:9">
+      <c r="I64">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="65" customFormat="1" spans="1:8">
       <c r="A65" t="s">
-        <v>433</v>
+        <v>591</v>
       </c>
       <c r="B65" t="s">
-        <v>9</v>
-      </c>
-      <c r="C65" t="s">
-        <v>445</v>
-      </c>
-      <c r="E65" t="s">
-        <v>446</v>
+        <v>138</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>573</v>
       </c>
       <c r="F65" t="s">
-        <v>905</v>
+        <v>943</v>
       </c>
       <c r="H65">
         <v>1</v>
-      </c>
-      <c r="I65">
-        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" t="s">
-        <v>433</v>
+        <v>938</v>
       </c>
       <c r="B66" t="s">
-        <v>361</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="C66" s="2"/>
       <c r="F66" t="s">
-        <v>361</v>
-      </c>
-      <c r="G66">
-        <v>3</v>
+        <v>928</v>
       </c>
       <c r="H66">
         <v>1</v>
       </c>
     </row>
-    <row r="67" customFormat="1" spans="1:8">
+    <row r="67" spans="1:8">
       <c r="A67" t="s">
-        <v>143</v>
+        <v>944</v>
       </c>
       <c r="B67" t="s">
-        <v>361</v>
-      </c>
+        <v>138</v>
+      </c>
+      <c r="C67" s="2"/>
       <c r="F67" t="s">
-        <v>361</v>
-      </c>
-      <c r="G67">
-        <v>3</v>
+        <v>928</v>
       </c>
       <c r="H67">
         <v>1</v>
@@ -21889,16 +21947,16 @@
     </row>
     <row r="68" spans="1:8">
       <c r="A68" t="s">
-        <v>932</v>
+        <v>133</v>
       </c>
       <c r="B68" t="s">
-        <v>938</v>
-      </c>
-      <c r="C68" t="s">
-        <v>933</v>
-      </c>
-      <c r="E68" t="s">
-        <v>934</v>
+        <v>944</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>136</v>
       </c>
       <c r="F68" t="s">
         <v>905</v>
@@ -21909,19 +21967,22 @@
     </row>
     <row r="69" spans="1:8">
       <c r="A69" t="s">
+        <v>138</v>
+      </c>
+      <c r="B69" t="s">
+        <v>931</v>
+      </c>
+      <c r="C69" t="s">
+        <v>66</v>
+      </c>
+      <c r="E69" t="s">
+        <v>138</v>
+      </c>
+      <c r="F69" t="s">
         <v>932</v>
       </c>
-      <c r="B69" t="s">
-        <v>938</v>
-      </c>
-      <c r="C69" t="s">
-        <v>935</v>
-      </c>
-      <c r="E69" t="s">
-        <v>344</v>
-      </c>
-      <c r="F69" t="s">
-        <v>905</v>
+      <c r="G69">
+        <v>180</v>
       </c>
       <c r="H69">
         <v>1</v>
@@ -21929,48 +21990,44 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70" t="s">
-        <v>185</v>
+        <v>931</v>
       </c>
       <c r="B70" t="s">
-        <v>188</v>
-      </c>
-      <c r="C70" s="2"/>
-      <c r="E70" s="2" t="s">
-        <v>188</v>
+        <v>433</v>
       </c>
       <c r="F70" t="s">
-        <v>905</v>
+        <v>928</v>
       </c>
       <c r="H70">
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" customFormat="1" spans="1:8">
       <c r="A71" t="s">
-        <v>185</v>
+        <v>931</v>
       </c>
       <c r="B71" t="s">
-        <v>189</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>189</v>
+        <v>143</v>
       </c>
       <c r="F71" t="s">
-        <v>905</v>
+        <v>928</v>
       </c>
       <c r="H71">
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:9">
       <c r="A72" t="s">
-        <v>185</v>
+        <v>433</v>
       </c>
       <c r="B72" t="s">
-        <v>190</v>
-      </c>
-      <c r="E72" s="3" t="s">
-        <v>190</v>
+        <v>9</v>
+      </c>
+      <c r="C72" t="s">
+        <v>445</v>
+      </c>
+      <c r="E72" t="s">
+        <v>446</v>
       </c>
       <c r="F72" t="s">
         <v>905</v>
@@ -21978,50 +22035,56 @@
       <c r="H72">
         <v>1</v>
       </c>
+      <c r="I72">
+        <v>5</v>
+      </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" t="s">
-        <v>185</v>
+        <v>433</v>
       </c>
       <c r="B73" t="s">
-        <v>192</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>192</v>
+        <v>361</v>
       </c>
       <c r="F73" t="s">
-        <v>905</v>
+        <v>361</v>
+      </c>
+      <c r="G73">
+        <v>3</v>
       </c>
       <c r="H73">
         <v>1</v>
       </c>
     </row>
-    <row r="74" ht="14.25" spans="1:8">
+    <row r="74" customFormat="1" spans="1:8">
       <c r="A74" t="s">
-        <v>185</v>
+        <v>143</v>
       </c>
       <c r="B74" t="s">
-        <v>193</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>193</v>
+        <v>361</v>
       </c>
       <c r="F74" t="s">
-        <v>905</v>
+        <v>361</v>
+      </c>
+      <c r="G74">
+        <v>3</v>
       </c>
       <c r="H74">
         <v>1</v>
       </c>
     </row>
-    <row r="75" ht="14.25" spans="1:8">
+    <row r="75" spans="1:8">
       <c r="A75" t="s">
-        <v>185</v>
+        <v>939</v>
       </c>
       <c r="B75" t="s">
-        <v>194</v>
-      </c>
-      <c r="E75" s="8" t="s">
-        <v>194</v>
+        <v>945</v>
+      </c>
+      <c r="C75" t="s">
+        <v>940</v>
+      </c>
+      <c r="E75" t="s">
+        <v>941</v>
       </c>
       <c r="F75" t="s">
         <v>905</v>
@@ -22030,15 +22093,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" ht="14.25" spans="1:8">
+    <row r="76" spans="1:8">
       <c r="A76" t="s">
-        <v>185</v>
+        <v>939</v>
       </c>
       <c r="B76" t="s">
-        <v>195</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>195</v>
+        <v>945</v>
+      </c>
+      <c r="C76" t="s">
+        <v>942</v>
+      </c>
+      <c r="E76" t="s">
+        <v>344</v>
       </c>
       <c r="F76" t="s">
         <v>905</v>
@@ -22047,15 +22113,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" ht="14.25" spans="1:8">
+    <row r="77" spans="1:8">
       <c r="A77" t="s">
         <v>185</v>
       </c>
       <c r="B77" t="s">
-        <v>290</v>
-      </c>
-      <c r="E77" s="4" t="s">
-        <v>198</v>
+        <v>188</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="E77" s="2" t="s">
+        <v>188</v>
       </c>
       <c r="F77" t="s">
         <v>905</v>
@@ -22069,10 +22136,10 @@
         <v>185</v>
       </c>
       <c r="B78" t="s">
-        <v>301</v>
+        <v>189</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>19</v>
+        <v>189</v>
       </c>
       <c r="F78" t="s">
         <v>905</v>
@@ -22086,10 +22153,10 @@
         <v>185</v>
       </c>
       <c r="B79" t="s">
-        <v>200</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>200</v>
+        <v>190</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>190</v>
       </c>
       <c r="F79" t="s">
         <v>905</v>
@@ -22103,44 +22170,44 @@
         <v>185</v>
       </c>
       <c r="B80" t="s">
-        <v>326</v>
+        <v>192</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>326</v>
+        <v>192</v>
       </c>
       <c r="F80" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="H80">
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:8">
+    <row r="81" ht="14.25" spans="1:8">
       <c r="A81" t="s">
         <v>185</v>
       </c>
       <c r="B81" t="s">
-        <v>939</v>
-      </c>
-      <c r="E81" s="3" t="s">
-        <v>939</v>
+        <v>193</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>193</v>
       </c>
       <c r="F81" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="H81">
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:8">
+    <row r="82" ht="14.25" spans="1:8">
       <c r="A82" t="s">
         <v>185</v>
       </c>
       <c r="B82" t="s">
-        <v>939</v>
-      </c>
-      <c r="E82" s="3" t="s">
-        <v>940</v>
+        <v>194</v>
+      </c>
+      <c r="E82" s="8" t="s">
+        <v>194</v>
       </c>
       <c r="F82" t="s">
         <v>905</v>
@@ -22149,35 +22216,35 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" ht="14.25" spans="1:8">
       <c r="A83" t="s">
         <v>185</v>
       </c>
       <c r="B83" t="s">
-        <v>939</v>
+        <v>195</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>941</v>
+        <v>195</v>
       </c>
       <c r="F83" t="s">
-        <v>925</v>
+        <v>905</v>
       </c>
       <c r="H83">
         <v>1</v>
       </c>
     </row>
-    <row r="84" customFormat="1" spans="1:8">
+    <row r="84" ht="14.25" spans="1:8">
       <c r="A84" t="s">
         <v>185</v>
       </c>
       <c r="B84" t="s">
-        <v>939</v>
-      </c>
-      <c r="E84" s="3" t="s">
-        <v>942</v>
+        <v>290</v>
+      </c>
+      <c r="E84" s="4" t="s">
+        <v>198</v>
       </c>
       <c r="F84" t="s">
-        <v>925</v>
+        <v>905</v>
       </c>
       <c r="H84">
         <v>1</v>
@@ -22188,10 +22255,10 @@
         <v>185</v>
       </c>
       <c r="B85" t="s">
-        <v>338</v>
+        <v>301</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>943</v>
+        <v>19</v>
       </c>
       <c r="F85" t="s">
         <v>905</v>
@@ -22205,13 +22272,10 @@
         <v>185</v>
       </c>
       <c r="B86" t="s">
-        <v>346</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>944</v>
+        <v>200</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>346</v>
+        <v>200</v>
       </c>
       <c r="F86" t="s">
         <v>905</v>
@@ -22225,50 +22289,45 @@
         <v>185</v>
       </c>
       <c r="B87" t="s">
-        <v>516</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="E87" s="3" t="s">
-        <v>516</v>
+        <v>326</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>326</v>
       </c>
       <c r="F87" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="H87">
         <v>1</v>
       </c>
     </row>
-    <row r="88" ht="14.25" spans="1:8">
+    <row r="88" spans="1:8">
       <c r="A88" t="s">
         <v>185</v>
       </c>
       <c r="B88" t="s">
-        <v>945</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="E88" s="3"/>
+        <v>946</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>946</v>
+      </c>
       <c r="F88" t="s">
+        <v>907</v>
+      </c>
+      <c r="H88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
+      <c r="A89" t="s">
+        <v>185</v>
+      </c>
+      <c r="B89" t="s">
         <v>946</v>
       </c>
-      <c r="H88">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="89" ht="14.25" spans="1:8">
-      <c r="A89" t="s">
-        <v>188</v>
-      </c>
-      <c r="B89" t="s">
-        <v>185</v>
-      </c>
-      <c r="C89" s="4" t="s">
+      <c r="E89" s="3" t="s">
         <v>947</v>
       </c>
-      <c r="E89" s="2"/>
       <c r="F89" t="s">
         <v>905</v>
       </c>
@@ -22276,35 +22335,35 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" ht="14.25" spans="1:8">
+    <row r="90" spans="1:8">
       <c r="A90" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B90" t="s">
+        <v>946</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>948</v>
+      </c>
+      <c r="F90" t="s">
+        <v>932</v>
+      </c>
+      <c r="H90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" customFormat="1" spans="1:8">
+      <c r="A91" t="s">
         <v>185</v>
       </c>
-      <c r="C90" s="2" t="s">
-        <v>947</v>
-      </c>
-      <c r="F90" t="s">
-        <v>905</v>
-      </c>
-      <c r="H90">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="91" ht="14.25" spans="1:8">
-      <c r="A91" t="s">
-        <v>190</v>
-      </c>
       <c r="B91" t="s">
-        <v>185</v>
-      </c>
-      <c r="C91" s="4" t="s">
-        <v>947</v>
+        <v>946</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>949</v>
       </c>
       <c r="F91" t="s">
-        <v>905</v>
+        <v>932</v>
       </c>
       <c r="H91">
         <v>1</v>
@@ -22312,13 +22371,13 @@
     </row>
     <row r="92" spans="1:8">
       <c r="A92" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="B92" t="s">
-        <v>185</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>947</v>
+        <v>338</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>950</v>
       </c>
       <c r="F92" t="s">
         <v>905</v>
@@ -22329,13 +22388,16 @@
     </row>
     <row r="93" spans="1:8">
       <c r="A93" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="B93" t="s">
-        <v>185</v>
+        <v>346</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>486</v>
+        <v>951</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>346</v>
       </c>
       <c r="F93" t="s">
         <v>905</v>
@@ -22344,15 +22406,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" ht="14.25" spans="1:8">
+    <row r="94" spans="1:8">
       <c r="A94" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="B94" t="s">
-        <v>185</v>
+        <v>516</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>486</v>
+        <v>187</v>
+      </c>
+      <c r="E94" s="3" t="s">
+        <v>516</v>
       </c>
       <c r="F94" t="s">
         <v>905</v>
@@ -22363,31 +22428,33 @@
     </row>
     <row r="95" ht="14.25" spans="1:8">
       <c r="A95" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="B95" t="s">
-        <v>185</v>
-      </c>
-      <c r="C95" s="4" t="s">
-        <v>947</v>
-      </c>
+        <v>952</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E95" s="3"/>
       <c r="F95" t="s">
-        <v>905</v>
+        <v>953</v>
       </c>
       <c r="H95">
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:8">
+    <row r="96" ht="14.25" spans="1:8">
       <c r="A96" t="s">
-        <v>290</v>
+        <v>188</v>
       </c>
       <c r="B96" t="s">
         <v>185</v>
       </c>
-      <c r="C96" s="2" t="s">
-        <v>486</v>
-      </c>
+      <c r="C96" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="E96" s="2"/>
       <c r="F96" t="s">
         <v>905</v>
       </c>
@@ -22395,15 +22462,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:8">
+    <row r="97" ht="14.25" spans="1:8">
       <c r="A97" t="s">
-        <v>301</v>
+        <v>189</v>
       </c>
       <c r="B97" t="s">
         <v>185</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>486</v>
+        <v>954</v>
       </c>
       <c r="F97" t="s">
         <v>905</v>
@@ -22412,15 +22479,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:8">
+    <row r="98" ht="14.25" spans="1:8">
       <c r="A98" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="B98" t="s">
         <v>185</v>
       </c>
-      <c r="C98" s="2" t="s">
-        <v>486</v>
+      <c r="C98" s="4" t="s">
+        <v>954</v>
       </c>
       <c r="F98" t="s">
         <v>905</v>
@@ -22431,13 +22498,13 @@
     </row>
     <row r="99" spans="1:8">
       <c r="A99" t="s">
-        <v>326</v>
+        <v>192</v>
       </c>
       <c r="B99" t="s">
         <v>185</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>947</v>
+        <v>954</v>
       </c>
       <c r="F99" t="s">
         <v>905</v>
@@ -22448,16 +22515,13 @@
     </row>
     <row r="100" spans="1:8">
       <c r="A100" t="s">
-        <v>338</v>
+        <v>193</v>
       </c>
       <c r="B100" t="s">
         <v>185</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>342</v>
+        <v>486</v>
       </c>
       <c r="F100" t="s">
         <v>905</v>
@@ -22466,18 +22530,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:8">
+    <row r="101" ht="14.25" spans="1:8">
       <c r="A101" t="s">
-        <v>346</v>
+        <v>194</v>
       </c>
       <c r="B101" t="s">
         <v>185</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>355</v>
+        <v>486</v>
       </c>
       <c r="F101" t="s">
         <v>905</v>
@@ -22486,18 +22547,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:8">
+    <row r="102" ht="14.25" spans="1:8">
       <c r="A102" t="s">
-        <v>356</v>
+        <v>195</v>
       </c>
       <c r="B102" t="s">
-        <v>21</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>948</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>21</v>
+        <v>185</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>954</v>
       </c>
       <c r="F102" t="s">
         <v>905</v>
@@ -22508,13 +22566,13 @@
     </row>
     <row r="103" spans="1:8">
       <c r="A103" t="s">
-        <v>356</v>
+        <v>290</v>
       </c>
       <c r="B103" t="s">
-        <v>9</v>
+        <v>185</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>947</v>
+        <v>486</v>
       </c>
       <c r="F103" t="s">
         <v>905</v>
@@ -22525,51 +22583,47 @@
     </row>
     <row r="104" spans="1:8">
       <c r="A104" t="s">
-        <v>356</v>
+        <v>301</v>
       </c>
       <c r="B104" t="s">
-        <v>949</v>
+        <v>185</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>950</v>
+        <v>486</v>
       </c>
       <c r="F104" t="s">
-        <v>919</v>
+        <v>905</v>
       </c>
       <c r="H104">
         <v>1</v>
       </c>
     </row>
-    <row r="105" ht="14.25" spans="1:8">
+    <row r="105" spans="1:8">
       <c r="A105" t="s">
-        <v>356</v>
+        <v>200</v>
       </c>
       <c r="B105" t="s">
-        <v>949</v>
+        <v>185</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="E105" s="2"/>
+        <v>486</v>
+      </c>
       <c r="F105" t="s">
-        <v>920</v>
+        <v>905</v>
       </c>
       <c r="H105">
         <v>1</v>
       </c>
     </row>
-    <row r="106" ht="14.25" spans="1:8">
+    <row r="106" spans="1:8">
       <c r="A106" t="s">
-        <v>21</v>
+        <v>326</v>
       </c>
       <c r="B106" t="s">
-        <v>356</v>
-      </c>
-      <c r="C106" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="E106" s="2" t="s">
-        <v>356</v>
+        <v>185</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>954</v>
       </c>
       <c r="F106" t="s">
         <v>905</v>
@@ -22580,13 +22634,16 @@
     </row>
     <row r="107" spans="1:8">
       <c r="A107" t="s">
-        <v>21</v>
+        <v>338</v>
       </c>
       <c r="B107" t="s">
-        <v>9</v>
+        <v>185</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>947</v>
+        <v>341</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>342</v>
       </c>
       <c r="F107" t="s">
         <v>905</v>
@@ -22597,16 +22654,16 @@
     </row>
     <row r="108" spans="1:8">
       <c r="A108" t="s">
-        <v>21</v>
+        <v>346</v>
       </c>
       <c r="B108" t="s">
-        <v>366</v>
+        <v>185</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="E108" s="2" t="s">
-        <v>366</v>
+        <v>354</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>355</v>
       </c>
       <c r="F108" t="s">
         <v>905</v>
@@ -22617,16 +22674,16 @@
     </row>
     <row r="109" spans="1:8">
       <c r="A109" t="s">
+        <v>356</v>
+      </c>
+      <c r="B109" t="s">
         <v>21</v>
       </c>
-      <c r="B109" t="s">
-        <v>368</v>
-      </c>
       <c r="C109" s="2" t="s">
-        <v>367</v>
+        <v>955</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>368</v>
+        <v>21</v>
       </c>
       <c r="F109" t="s">
         <v>905</v>
@@ -22637,13 +22694,13 @@
     </row>
     <row r="110" spans="1:8">
       <c r="A110" t="s">
-        <v>35</v>
+        <v>356</v>
       </c>
       <c r="B110" t="s">
         <v>9</v>
       </c>
-      <c r="E110" s="2" t="s">
-        <v>9</v>
+      <c r="C110" s="2" t="s">
+        <v>954</v>
       </c>
       <c r="F110" t="s">
         <v>905</v>
@@ -22654,49 +22711,52 @@
     </row>
     <row r="111" spans="1:8">
       <c r="A111" t="s">
-        <v>35</v>
+        <v>356</v>
       </c>
       <c r="B111" t="s">
-        <v>380</v>
-      </c>
-      <c r="E111" s="3" t="s">
-        <v>380</v>
+        <v>956</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>957</v>
       </c>
       <c r="F111" t="s">
-        <v>905</v>
+        <v>913</v>
       </c>
       <c r="H111">
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:8">
+    <row r="112" ht="14.25" spans="1:8">
       <c r="A112" t="s">
-        <v>35</v>
+        <v>356</v>
       </c>
       <c r="B112" t="s">
-        <v>64</v>
-      </c>
-      <c r="E112" s="3" t="s">
-        <v>64</v>
-      </c>
+        <v>956</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="E112" s="2"/>
       <c r="F112" t="s">
-        <v>905</v>
+        <v>927</v>
       </c>
       <c r="H112">
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:8">
+    <row r="113" ht="14.25" spans="1:8">
       <c r="A113" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="B113" t="s">
-        <v>951</v>
-      </c>
-      <c r="C113" t="s">
-        <v>952</v>
-      </c>
-      <c r="E113" s="3"/>
+        <v>356</v>
+      </c>
+      <c r="C113" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>356</v>
+      </c>
       <c r="F113" t="s">
         <v>905</v>
       </c>
@@ -22706,13 +22766,13 @@
     </row>
     <row r="114" spans="1:8">
       <c r="A114" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="B114" t="s">
-        <v>951</v>
-      </c>
-      <c r="E114" s="3" t="s">
-        <v>335</v>
+        <v>9</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>954</v>
       </c>
       <c r="F114" t="s">
         <v>905</v>
@@ -22721,15 +22781,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:9">
+    <row r="115" spans="1:8">
       <c r="A115" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="B115" t="s">
-        <v>951</v>
-      </c>
-      <c r="E115" s="3" t="s">
-        <v>953</v>
+        <v>366</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>366</v>
       </c>
       <c r="F115" t="s">
         <v>905</v>
@@ -22737,19 +22800,19 @@
       <c r="H115">
         <v>1</v>
       </c>
-      <c r="I115">
-        <v>3</v>
-      </c>
     </row>
     <row r="116" spans="1:8">
       <c r="A116" t="s">
-        <v>64</v>
+        <v>21</v>
       </c>
       <c r="B116" t="s">
-        <v>951</v>
-      </c>
-      <c r="E116" s="3" t="s">
-        <v>954</v>
+        <v>368</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>368</v>
       </c>
       <c r="F116" t="s">
         <v>905</v>
@@ -22760,13 +22823,13 @@
     </row>
     <row r="117" spans="1:8">
       <c r="A117" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="B117" t="s">
-        <v>951</v>
-      </c>
-      <c r="E117" s="3" t="s">
-        <v>955</v>
+        <v>9</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="F117" t="s">
         <v>905</v>
@@ -22777,15 +22840,14 @@
     </row>
     <row r="118" spans="1:8">
       <c r="A118" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="B118" t="s">
-        <v>956</v>
-      </c>
-      <c r="C118" t="s">
-        <v>780</v>
-      </c>
-      <c r="E118" s="3"/>
+        <v>380</v>
+      </c>
+      <c r="E118" s="3" t="s">
+        <v>380</v>
+      </c>
       <c r="F118" t="s">
         <v>905</v>
       </c>
@@ -22795,13 +22857,13 @@
     </row>
     <row r="119" spans="1:8">
       <c r="A119" t="s">
+        <v>35</v>
+      </c>
+      <c r="B119" t="s">
         <v>64</v>
       </c>
-      <c r="B119" t="s">
-        <v>956</v>
-      </c>
       <c r="E119" s="3" t="s">
-        <v>957</v>
+        <v>64</v>
       </c>
       <c r="F119" t="s">
         <v>905</v>
@@ -22815,11 +22877,12 @@
         <v>64</v>
       </c>
       <c r="B120" t="s">
-        <v>956</v>
-      </c>
-      <c r="E120" s="3" t="s">
         <v>958</v>
       </c>
+      <c r="C120" t="s">
+        <v>959</v>
+      </c>
+      <c r="E120" s="3"/>
       <c r="F120" t="s">
         <v>905</v>
       </c>
@@ -22832,10 +22895,10 @@
         <v>64</v>
       </c>
       <c r="B121" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>959</v>
+        <v>335</v>
       </c>
       <c r="F121" t="s">
         <v>905</v>
@@ -22844,15 +22907,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:8">
+    <row r="122" spans="1:9">
       <c r="A122" t="s">
-        <v>380</v>
+        <v>64</v>
       </c>
       <c r="B122" t="s">
-        <v>35</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>947</v>
+        <v>958</v>
+      </c>
+      <c r="E122" s="3" t="s">
+        <v>960</v>
       </c>
       <c r="F122" t="s">
         <v>905</v>
@@ -22860,19 +22923,19 @@
       <c r="H122">
         <v>1</v>
       </c>
-    </row>
-    <row r="123" ht="14.25" spans="1:8">
+      <c r="I122">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8">
       <c r="A123" t="s">
-        <v>380</v>
+        <v>64</v>
       </c>
       <c r="B123" t="s">
-        <v>392</v>
-      </c>
-      <c r="C123" s="2" t="s">
-        <v>390</v>
+        <v>958</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="F123" t="s">
         <v>905</v>
@@ -22881,18 +22944,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" ht="14.25" spans="1:8">
+    <row r="124" spans="1:8">
       <c r="A124" t="s">
-        <v>380</v>
+        <v>64</v>
       </c>
       <c r="B124" t="s">
-        <v>392</v>
-      </c>
-      <c r="C124" s="2" t="s">
-        <v>961</v>
-      </c>
-      <c r="E124" s="4" t="s">
-        <v>344</v>
+        <v>958</v>
+      </c>
+      <c r="E124" s="3" t="s">
+        <v>962</v>
       </c>
       <c r="F124" t="s">
         <v>905</v>
@@ -22903,15 +22963,15 @@
     </row>
     <row r="125" spans="1:8">
       <c r="A125" t="s">
-        <v>380</v>
+        <v>64</v>
       </c>
       <c r="B125" t="s">
-        <v>389</v>
-      </c>
-      <c r="C125" s="2"/>
-      <c r="E125" s="6" t="s">
-        <v>389</v>
-      </c>
+        <v>963</v>
+      </c>
+      <c r="C125" t="s">
+        <v>780</v>
+      </c>
+      <c r="E125" s="3"/>
       <c r="F125" t="s">
         <v>905</v>
       </c>
@@ -22921,16 +22981,13 @@
     </row>
     <row r="126" spans="1:8">
       <c r="A126" t="s">
-        <v>380</v>
+        <v>64</v>
       </c>
       <c r="B126" t="s">
-        <v>389</v>
-      </c>
-      <c r="C126" s="2" t="s">
-        <v>962</v>
-      </c>
-      <c r="E126" s="6" t="s">
         <v>963</v>
+      </c>
+      <c r="E126" s="3" t="s">
+        <v>964</v>
       </c>
       <c r="F126" t="s">
         <v>905</v>
@@ -22939,18 +22996,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" customFormat="1" spans="1:8">
+    <row r="127" spans="1:8">
       <c r="A127" t="s">
-        <v>380</v>
+        <v>64</v>
       </c>
       <c r="B127" t="s">
-        <v>389</v>
-      </c>
-      <c r="C127" s="2" t="s">
-        <v>961</v>
-      </c>
-      <c r="E127" s="6" t="s">
-        <v>344</v>
+        <v>963</v>
+      </c>
+      <c r="E127" s="3" t="s">
+        <v>965</v>
       </c>
       <c r="F127" t="s">
         <v>905</v>
@@ -22959,16 +23013,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" customFormat="1" spans="1:9">
+    <row r="128" spans="1:8">
       <c r="A128" t="s">
-        <v>389</v>
+        <v>64</v>
       </c>
       <c r="B128" t="s">
-        <v>699</v>
-      </c>
-      <c r="C128" s="2"/>
-      <c r="E128" s="6" t="s">
-        <v>699</v>
+        <v>963</v>
+      </c>
+      <c r="E128" s="3" t="s">
+        <v>966</v>
       </c>
       <c r="F128" t="s">
         <v>905</v>
@@ -22976,38 +23029,36 @@
       <c r="H128">
         <v>1</v>
       </c>
-      <c r="I128">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="129" customFormat="1" spans="1:8">
+    </row>
+    <row r="129" spans="1:8">
       <c r="A129" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="B129" t="s">
-        <v>964</v>
+        <v>35</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>694</v>
-      </c>
-      <c r="E129" s="6"/>
+        <v>954</v>
+      </c>
       <c r="F129" t="s">
-        <v>912</v>
+        <v>905</v>
       </c>
       <c r="H129">
         <v>1</v>
       </c>
     </row>
-    <row r="130" customFormat="1" spans="1:8">
+    <row r="130" ht="14.25" spans="1:8">
       <c r="A130" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="B130" t="s">
-        <v>964</v>
-      </c>
-      <c r="C130" s="2"/>
-      <c r="E130" s="7" t="s">
-        <v>446</v>
+        <v>392</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="E130" s="3" t="s">
+        <v>967</v>
       </c>
       <c r="F130" t="s">
         <v>905</v>
@@ -23016,17 +23067,19 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" customFormat="1" spans="1:8">
+    <row r="131" ht="14.25" spans="1:8">
       <c r="A131" t="s">
+        <v>380</v>
+      </c>
+      <c r="B131" t="s">
         <v>392</v>
       </c>
-      <c r="B131" t="s">
-        <v>9</v>
-      </c>
       <c r="C131" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="E131" s="2"/>
+        <v>968</v>
+      </c>
+      <c r="E131" s="4" t="s">
+        <v>344</v>
+      </c>
       <c r="F131" t="s">
         <v>905</v>
       </c>
@@ -23034,16 +23087,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" customFormat="1" spans="1:8">
+    <row r="132" spans="1:8">
       <c r="A132" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="B132" t="s">
-        <v>9</v>
+        <v>389</v>
       </c>
       <c r="C132" s="2"/>
-      <c r="E132" t="s">
-        <v>388</v>
+      <c r="E132" s="6" t="s">
+        <v>389</v>
       </c>
       <c r="F132" t="s">
         <v>905</v>
@@ -23054,48 +23107,54 @@
     </row>
     <row r="133" spans="1:8">
       <c r="A133" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="B133" t="s">
-        <v>9</v>
+        <v>389</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="E133" s="2"/>
+        <v>969</v>
+      </c>
+      <c r="E133" s="6" t="s">
+        <v>970</v>
+      </c>
       <c r="F133" t="s">
-        <v>912</v>
+        <v>905</v>
       </c>
       <c r="H133">
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:8">
+    <row r="134" customFormat="1" spans="1:8">
       <c r="A134" t="s">
-        <v>392</v>
+        <v>380</v>
       </c>
       <c r="B134" t="s">
-        <v>9</v>
+        <v>389</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>399</v>
+        <v>968</v>
+      </c>
+      <c r="E134" s="6" t="s">
+        <v>344</v>
       </c>
       <c r="F134" t="s">
-        <v>912</v>
+        <v>905</v>
       </c>
       <c r="H134">
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:8">
+    <row r="135" customFormat="1" spans="1:9">
       <c r="A135" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B135" t="s">
-        <v>9</v>
-      </c>
-      <c r="C135" s="2" t="s">
-        <v>965</v>
+        <v>699</v>
+      </c>
+      <c r="C135" s="2"/>
+      <c r="E135" s="6" t="s">
+        <v>699</v>
       </c>
       <c r="F135" t="s">
         <v>905</v>
@@ -23103,36 +23162,38 @@
       <c r="H135">
         <v>1</v>
       </c>
-    </row>
-    <row r="136" spans="1:9">
+      <c r="I135">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="136" customFormat="1" spans="1:8">
       <c r="A136" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B136" t="s">
-        <v>9</v>
+        <v>971</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>403</v>
-      </c>
+        <v>694</v>
+      </c>
+      <c r="E136" s="6"/>
       <c r="F136" t="s">
-        <v>905</v>
+        <v>920</v>
       </c>
       <c r="H136">
         <v>1</v>
       </c>
-      <c r="I136">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8">
+    </row>
+    <row r="137" customFormat="1" spans="1:8">
       <c r="A137" t="s">
-        <v>450</v>
+        <v>389</v>
       </c>
       <c r="B137" t="s">
-        <v>9</v>
-      </c>
-      <c r="C137" s="2" t="s">
-        <v>478</v>
+        <v>971</v>
+      </c>
+      <c r="C137" s="2"/>
+      <c r="E137" s="7" t="s">
+        <v>446</v>
       </c>
       <c r="F137" t="s">
         <v>905</v>
@@ -23141,38 +23202,36 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:8">
+    <row r="138" customFormat="1" spans="1:8">
       <c r="A138" t="s">
-        <v>356</v>
+        <v>392</v>
       </c>
       <c r="B138" t="s">
-        <v>361</v>
-      </c>
+        <v>972</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="E138" s="2"/>
       <c r="F138" t="s">
-        <v>361</v>
-      </c>
-      <c r="G138">
-        <v>3</v>
+        <v>905</v>
       </c>
       <c r="H138">
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:8">
+    <row r="139" customFormat="1" spans="1:8">
       <c r="A139" t="s">
-        <v>22</v>
+        <v>392</v>
       </c>
       <c r="B139" t="s">
-        <v>966</v>
+        <v>972</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>967</v>
-      </c>
-      <c r="E139" t="s">
-        <v>966</v>
+        <v>327</v>
       </c>
       <c r="F139" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="H139">
         <v>1</v>
@@ -23180,37 +23239,34 @@
     </row>
     <row r="140" spans="1:8">
       <c r="A140" t="s">
-        <v>22</v>
+        <v>392</v>
       </c>
       <c r="B140" t="s">
-        <v>966</v>
+        <v>9</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>935</v>
-      </c>
-      <c r="E140" s="2" t="s">
-        <v>344</v>
-      </c>
+        <v>397</v>
+      </c>
+      <c r="E140" s="2"/>
       <c r="F140" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="H140">
         <v>1</v>
       </c>
     </row>
-    <row r="141" customFormat="1" spans="1:8">
+    <row r="141" spans="1:8">
       <c r="A141" t="s">
-        <v>22</v>
+        <v>392</v>
       </c>
       <c r="B141" t="s">
-        <v>966</v>
-      </c>
-      <c r="C141" s="2"/>
-      <c r="E141" s="3" t="s">
-        <v>353</v>
+        <v>9</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>399</v>
       </c>
       <c r="F141" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="H141">
         <v>1</v>
@@ -23218,47 +23274,50 @@
     </row>
     <row r="142" spans="1:8">
       <c r="A142" t="s">
-        <v>185</v>
+        <v>392</v>
       </c>
       <c r="B142" t="s">
-        <v>361</v>
+        <v>9</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>973</v>
       </c>
       <c r="F142" t="s">
-        <v>361</v>
-      </c>
-      <c r="G142">
+        <v>905</v>
+      </c>
+      <c r="H142">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="143" spans="1:9">
+      <c r="A143" t="s">
+        <v>392</v>
+      </c>
+      <c r="B143" t="s">
+        <v>9</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="F143" t="s">
+        <v>905</v>
+      </c>
+      <c r="H143">
+        <v>1</v>
+      </c>
+      <c r="I143">
         <v>3</v>
-      </c>
-      <c r="H142">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="143" spans="1:8">
-      <c r="A143" t="s">
-        <v>21</v>
-      </c>
-      <c r="B143" t="s">
-        <v>361</v>
-      </c>
-      <c r="F143" t="s">
-        <v>361</v>
-      </c>
-      <c r="G143">
-        <v>3</v>
-      </c>
-      <c r="H143">
-        <v>1</v>
       </c>
     </row>
     <row r="144" spans="1:8">
       <c r="A144" t="s">
-        <v>21</v>
+        <v>450</v>
       </c>
       <c r="B144" t="s">
-        <v>762</v>
-      </c>
-      <c r="E144" t="s">
-        <v>762</v>
+        <v>9</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>478</v>
       </c>
       <c r="F144" t="s">
         <v>905</v>
@@ -23269,16 +23328,16 @@
     </row>
     <row r="145" spans="1:8">
       <c r="A145" t="s">
-        <v>21</v>
+        <v>356</v>
       </c>
       <c r="B145" t="s">
-        <v>723</v>
-      </c>
-      <c r="E145" t="s">
-        <v>723</v>
+        <v>361</v>
       </c>
       <c r="F145" t="s">
-        <v>905</v>
+        <v>361</v>
+      </c>
+      <c r="G145">
+        <v>3</v>
       </c>
       <c r="H145">
         <v>1</v>
@@ -23286,13 +23345,19 @@
     </row>
     <row r="146" spans="1:8">
       <c r="A146" t="s">
-        <v>762</v>
+        <v>22</v>
       </c>
       <c r="B146" t="s">
-        <v>21</v>
+        <v>974</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>975</v>
+      </c>
+      <c r="E146" t="s">
+        <v>974</v>
       </c>
       <c r="F146" t="s">
-        <v>921</v>
+        <v>905</v>
       </c>
       <c r="H146">
         <v>1</v>
@@ -23300,33 +23365,37 @@
     </row>
     <row r="147" spans="1:8">
       <c r="A147" t="s">
-        <v>723</v>
+        <v>22</v>
       </c>
       <c r="B147" t="s">
-        <v>21</v>
-      </c>
-      <c r="C147" t="s">
-        <v>968</v>
+        <v>974</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>942</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>344</v>
       </c>
       <c r="F147" t="s">
-        <v>905</v>
+        <v>913</v>
       </c>
       <c r="H147">
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:8">
+    <row r="148" customFormat="1" spans="1:8">
       <c r="A148" t="s">
-        <v>723</v>
+        <v>22</v>
       </c>
       <c r="B148" t="s">
-        <v>361</v>
+        <v>974</v>
+      </c>
+      <c r="C148" s="2"/>
+      <c r="E148" s="3" t="s">
+        <v>353</v>
       </c>
       <c r="F148" t="s">
-        <v>361</v>
-      </c>
-      <c r="G148">
-        <v>3</v>
+        <v>913</v>
       </c>
       <c r="H148">
         <v>1</v>
@@ -23334,16 +23403,16 @@
     </row>
     <row r="149" spans="1:8">
       <c r="A149" t="s">
-        <v>723</v>
+        <v>185</v>
       </c>
       <c r="B149" t="s">
-        <v>969</v>
-      </c>
-      <c r="C149" t="s">
-        <v>740</v>
+        <v>361</v>
       </c>
       <c r="F149" t="s">
-        <v>905</v>
+        <v>361</v>
+      </c>
+      <c r="G149">
+        <v>3</v>
       </c>
       <c r="H149">
         <v>1</v>
@@ -23351,16 +23420,16 @@
     </row>
     <row r="150" spans="1:8">
       <c r="A150" t="s">
-        <v>723</v>
+        <v>21</v>
       </c>
       <c r="B150" t="s">
-        <v>970</v>
-      </c>
-      <c r="C150" t="s">
-        <v>734</v>
+        <v>361</v>
       </c>
       <c r="F150" t="s">
-        <v>905</v>
+        <v>361</v>
+      </c>
+      <c r="G150">
+        <v>3</v>
       </c>
       <c r="H150">
         <v>1</v>
@@ -23368,13 +23437,16 @@
     </row>
     <row r="151" spans="1:8">
       <c r="A151" t="s">
-        <v>723</v>
+        <v>21</v>
       </c>
       <c r="B151" t="s">
-        <v>971</v>
+        <v>762</v>
+      </c>
+      <c r="E151" t="s">
+        <v>762</v>
       </c>
       <c r="F151" t="s">
-        <v>971</v>
+        <v>905</v>
       </c>
       <c r="H151">
         <v>1</v>
@@ -23382,13 +23454,13 @@
     </row>
     <row r="152" spans="1:8">
       <c r="A152" t="s">
+        <v>21</v>
+      </c>
+      <c r="B152" t="s">
         <v>723</v>
       </c>
-      <c r="B152" t="s">
-        <v>866</v>
-      </c>
-      <c r="C152" t="s">
-        <v>744</v>
+      <c r="E152" t="s">
+        <v>723</v>
       </c>
       <c r="F152" t="s">
         <v>905</v>
@@ -23399,27 +23471,30 @@
     </row>
     <row r="153" spans="1:8">
       <c r="A153" t="s">
-        <v>866</v>
+        <v>762</v>
       </c>
       <c r="B153" t="s">
-        <v>972</v>
+        <v>21</v>
       </c>
       <c r="F153" t="s">
-        <v>972</v>
+        <v>928</v>
       </c>
       <c r="H153">
         <v>1</v>
       </c>
     </row>
-    <row r="154" customFormat="1" spans="1:8">
+    <row r="154" spans="1:8">
       <c r="A154" t="s">
-        <v>866</v>
+        <v>723</v>
       </c>
       <c r="B154" t="s">
-        <v>973</v>
+        <v>21</v>
+      </c>
+      <c r="C154" t="s">
+        <v>976</v>
       </c>
       <c r="F154" t="s">
-        <v>973</v>
+        <v>905</v>
       </c>
       <c r="H154">
         <v>1</v>
@@ -23427,16 +23502,16 @@
     </row>
     <row r="155" spans="1:8">
       <c r="A155" t="s">
-        <v>866</v>
+        <v>723</v>
       </c>
       <c r="B155" t="s">
-        <v>723</v>
-      </c>
-      <c r="E155" t="s">
-        <v>344</v>
+        <v>361</v>
       </c>
       <c r="F155" t="s">
-        <v>905</v>
+        <v>361</v>
+      </c>
+      <c r="G155">
+        <v>3</v>
       </c>
       <c r="H155">
         <v>1</v>
@@ -23444,13 +23519,13 @@
     </row>
     <row r="156" spans="1:8">
       <c r="A156" t="s">
-        <v>516</v>
+        <v>723</v>
       </c>
       <c r="B156" t="s">
-        <v>974</v>
+        <v>977</v>
       </c>
       <c r="C156" t="s">
-        <v>523</v>
+        <v>740</v>
       </c>
       <c r="F156" t="s">
         <v>905</v>
@@ -23461,16 +23536,13 @@
     </row>
     <row r="157" spans="1:8">
       <c r="A157" t="s">
-        <v>326</v>
+        <v>723</v>
       </c>
       <c r="B157" t="s">
-        <v>975</v>
+        <v>978</v>
       </c>
       <c r="C157" t="s">
-        <v>334</v>
-      </c>
-      <c r="E157" t="s">
-        <v>335</v>
+        <v>734</v>
       </c>
       <c r="F157" t="s">
         <v>905</v>
@@ -23481,16 +23553,13 @@
     </row>
     <row r="158" spans="1:8">
       <c r="A158" t="s">
-        <v>326</v>
+        <v>723</v>
       </c>
       <c r="B158" t="s">
-        <v>975</v>
-      </c>
-      <c r="E158" t="s">
-        <v>976</v>
+        <v>979</v>
       </c>
       <c r="F158" t="s">
-        <v>905</v>
+        <v>979</v>
       </c>
       <c r="H158">
         <v>1</v>
@@ -23498,16 +23567,13 @@
     </row>
     <row r="159" spans="1:8">
       <c r="A159" t="s">
-        <v>185</v>
+        <v>723</v>
       </c>
       <c r="B159" t="s">
-        <v>977</v>
+        <v>866</v>
       </c>
       <c r="C159" t="s">
-        <v>187</v>
-      </c>
-      <c r="E159" t="s">
-        <v>977</v>
+        <v>744</v>
       </c>
       <c r="F159" t="s">
         <v>905</v>
@@ -23516,35 +23582,29 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" customFormat="1" spans="1:8">
+    <row r="160" spans="1:8">
       <c r="A160" t="s">
-        <v>185</v>
+        <v>866</v>
       </c>
       <c r="B160" t="s">
-        <v>977</v>
-      </c>
-      <c r="E160" t="s">
-        <v>940</v>
+        <v>980</v>
       </c>
       <c r="F160" t="s">
-        <v>905</v>
+        <v>980</v>
       </c>
       <c r="H160">
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:8">
+    <row r="161" customFormat="1" spans="1:8">
       <c r="A161" t="s">
-        <v>185</v>
+        <v>866</v>
       </c>
       <c r="B161" t="s">
-        <v>977</v>
-      </c>
-      <c r="E161" t="s">
-        <v>978</v>
+        <v>981</v>
       </c>
       <c r="F161" t="s">
-        <v>925</v>
+        <v>981</v>
       </c>
       <c r="H161">
         <v>1</v>
@@ -23552,13 +23612,13 @@
     </row>
     <row r="162" spans="1:8">
       <c r="A162" t="s">
-        <v>326</v>
+        <v>866</v>
       </c>
       <c r="B162" t="s">
-        <v>979</v>
+        <v>723</v>
       </c>
       <c r="E162" t="s">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="F162" t="s">
         <v>905</v>
@@ -23567,32 +23627,35 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" customFormat="1" spans="1:8">
+    <row r="163" spans="1:8">
       <c r="A163" t="s">
-        <v>326</v>
+        <v>516</v>
       </c>
       <c r="B163" t="s">
-        <v>979</v>
+        <v>982</v>
       </c>
       <c r="C163" t="s">
-        <v>980</v>
+        <v>523</v>
       </c>
       <c r="F163" t="s">
-        <v>912</v>
+        <v>905</v>
       </c>
       <c r="H163">
         <v>1</v>
       </c>
     </row>
-    <row r="164" customFormat="1" spans="1:8">
+    <row r="164" spans="1:8">
       <c r="A164" t="s">
         <v>326</v>
       </c>
       <c r="B164" t="s">
-        <v>979</v>
+        <v>983</v>
+      </c>
+      <c r="C164" t="s">
+        <v>334</v>
       </c>
       <c r="E164" t="s">
-        <v>981</v>
+        <v>335</v>
       </c>
       <c r="F164" t="s">
         <v>905</v>
@@ -23601,15 +23664,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" customFormat="1" spans="1:8">
+    <row r="165" spans="1:8">
       <c r="A165" t="s">
         <v>326</v>
       </c>
       <c r="B165" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="E165" t="s">
-        <v>958</v>
+        <v>984</v>
       </c>
       <c r="F165" t="s">
         <v>905</v>
@@ -23620,13 +23683,16 @@
     </row>
     <row r="166" spans="1:8">
       <c r="A166" t="s">
-        <v>702</v>
+        <v>185</v>
       </c>
       <c r="B166" t="s">
-        <v>712</v>
+        <v>985</v>
+      </c>
+      <c r="C166" t="s">
+        <v>187</v>
       </c>
       <c r="E166" t="s">
-        <v>712</v>
+        <v>985</v>
       </c>
       <c r="F166" t="s">
         <v>905</v>
@@ -23635,15 +23701,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:8">
+    <row r="167" customFormat="1" spans="1:8">
       <c r="A167" t="s">
-        <v>702</v>
+        <v>185</v>
       </c>
       <c r="B167" t="s">
-        <v>709</v>
+        <v>985</v>
       </c>
       <c r="E167" t="s">
-        <v>709</v>
+        <v>947</v>
       </c>
       <c r="F167" t="s">
         <v>905</v>
@@ -23654,30 +23720,30 @@
     </row>
     <row r="168" spans="1:8">
       <c r="A168" t="s">
-        <v>712</v>
+        <v>185</v>
       </c>
       <c r="B168" t="s">
-        <v>982</v>
-      </c>
-      <c r="C168" t="s">
-        <v>327</v>
+        <v>985</v>
+      </c>
+      <c r="E168" t="s">
+        <v>986</v>
       </c>
       <c r="F168" t="s">
-        <v>905</v>
+        <v>932</v>
       </c>
       <c r="H168">
         <v>1</v>
       </c>
     </row>
-    <row r="169" customFormat="1" spans="1:8">
+    <row r="169" spans="1:8">
       <c r="A169" t="s">
-        <v>712</v>
+        <v>326</v>
       </c>
       <c r="B169" t="s">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="E169" t="s">
-        <v>982</v>
+        <v>337</v>
       </c>
       <c r="F169" t="s">
         <v>905</v>
@@ -23686,49 +23752,49 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:8">
+    <row r="170" customFormat="1" spans="1:8">
       <c r="A170" t="s">
         <v>326</v>
       </c>
       <c r="B170" t="s">
-        <v>983</v>
+        <v>987</v>
       </c>
       <c r="C170" t="s">
-        <v>334</v>
+        <v>988</v>
       </c>
       <c r="F170" t="s">
-        <v>905</v>
+        <v>920</v>
       </c>
       <c r="H170">
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:8">
+    <row r="171" customFormat="1" spans="1:8">
       <c r="A171" t="s">
         <v>326</v>
       </c>
       <c r="B171" t="s">
-        <v>983</v>
-      </c>
-      <c r="C171" t="s">
-        <v>980</v>
+        <v>987</v>
+      </c>
+      <c r="E171" t="s">
+        <v>989</v>
       </c>
       <c r="F171" t="s">
-        <v>912</v>
+        <v>905</v>
       </c>
       <c r="H171">
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:8">
+    <row r="172" customFormat="1" spans="1:8">
       <c r="A172" t="s">
         <v>326</v>
       </c>
       <c r="B172" t="s">
-        <v>983</v>
-      </c>
-      <c r="C172" t="s">
-        <v>334</v>
+        <v>987</v>
+      </c>
+      <c r="E172" t="s">
+        <v>965</v>
       </c>
       <c r="F172" t="s">
         <v>905</v>
@@ -23739,13 +23805,13 @@
     </row>
     <row r="173" spans="1:8">
       <c r="A173" t="s">
-        <v>709</v>
+        <v>702</v>
       </c>
       <c r="B173" t="s">
-        <v>984</v>
-      </c>
-      <c r="C173" t="s">
-        <v>985</v>
+        <v>712</v>
+      </c>
+      <c r="E173" t="s">
+        <v>712</v>
       </c>
       <c r="F173" t="s">
         <v>905</v>
@@ -23754,15 +23820,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" customFormat="1" spans="1:8">
+    <row r="174" spans="1:8">
       <c r="A174" t="s">
+        <v>702</v>
+      </c>
+      <c r="B174" t="s">
         <v>709</v>
       </c>
-      <c r="B174" t="s">
-        <v>984</v>
-      </c>
-      <c r="C174" t="s">
-        <v>986</v>
+      <c r="E174" t="s">
+        <v>709</v>
       </c>
       <c r="F174" t="s">
         <v>905</v>
@@ -23771,15 +23837,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" customFormat="1" spans="1:8">
+    <row r="175" spans="1:8">
       <c r="A175" t="s">
-        <v>326</v>
+        <v>712</v>
       </c>
       <c r="B175" t="s">
-        <v>976</v>
-      </c>
-      <c r="E175" t="s">
-        <v>335</v>
+        <v>990</v>
+      </c>
+      <c r="C175" t="s">
+        <v>327</v>
       </c>
       <c r="F175" t="s">
         <v>905</v>
@@ -23788,15 +23854,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:8">
+    <row r="176" customFormat="1" spans="1:8">
       <c r="A176" t="s">
-        <v>326</v>
+        <v>712</v>
       </c>
       <c r="B176" t="s">
-        <v>976</v>
+        <v>990</v>
       </c>
       <c r="E176" t="s">
-        <v>976</v>
+        <v>990</v>
       </c>
       <c r="F176" t="s">
         <v>905</v>
@@ -23810,10 +23876,13 @@
         <v>326</v>
       </c>
       <c r="B177" t="s">
-        <v>976</v>
+        <v>991</v>
+      </c>
+      <c r="C177" t="s">
+        <v>334</v>
       </c>
       <c r="F177" t="s">
-        <v>361</v>
+        <v>905</v>
       </c>
       <c r="H177">
         <v>1</v>
@@ -23824,27 +23893,27 @@
         <v>326</v>
       </c>
       <c r="B178" t="s">
-        <v>987</v>
-      </c>
-      <c r="E178" t="s">
-        <v>335</v>
+        <v>991</v>
+      </c>
+      <c r="C178" t="s">
+        <v>988</v>
       </c>
       <c r="F178" t="s">
-        <v>905</v>
+        <v>920</v>
       </c>
       <c r="H178">
         <v>1</v>
       </c>
     </row>
-    <row r="179" customFormat="1" spans="1:9">
+    <row r="179" spans="1:8">
       <c r="A179" t="s">
         <v>326</v>
       </c>
       <c r="B179" t="s">
-        <v>987</v>
-      </c>
-      <c r="E179" t="s">
-        <v>987</v>
+        <v>991</v>
+      </c>
+      <c r="C179" t="s">
+        <v>334</v>
       </c>
       <c r="F179" t="s">
         <v>905</v>
@@ -23852,19 +23921,16 @@
       <c r="H179">
         <v>1</v>
       </c>
-      <c r="I179">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="180" customFormat="1" spans="1:8">
+    </row>
+    <row r="180" spans="1:8">
       <c r="A180" t="s">
-        <v>326</v>
+        <v>709</v>
       </c>
       <c r="B180" t="s">
-        <v>987</v>
-      </c>
-      <c r="E180" t="s">
-        <v>954</v>
+        <v>992</v>
+      </c>
+      <c r="C180" t="s">
+        <v>993</v>
       </c>
       <c r="F180" t="s">
         <v>905</v>
@@ -23873,15 +23939,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:8">
+    <row r="181" customFormat="1" spans="1:8">
       <c r="A181" t="s">
-        <v>326</v>
+        <v>709</v>
       </c>
       <c r="B181" t="s">
-        <v>987</v>
-      </c>
-      <c r="E181" t="s">
-        <v>335</v>
+        <v>992</v>
+      </c>
+      <c r="C181" t="s">
+        <v>994</v>
       </c>
       <c r="F181" t="s">
         <v>905</v>
@@ -23890,15 +23956,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:8">
+    <row r="182" customFormat="1" spans="1:8">
       <c r="A182" t="s">
         <v>326</v>
       </c>
       <c r="B182" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="E182" t="s">
-        <v>988</v>
+        <v>335</v>
       </c>
       <c r="F182" t="s">
         <v>905</v>
@@ -23912,10 +23978,10 @@
         <v>326</v>
       </c>
       <c r="B183" t="s">
-        <v>987</v>
+        <v>984</v>
       </c>
       <c r="E183" t="s">
-        <v>954</v>
+        <v>984</v>
       </c>
       <c r="F183" t="s">
         <v>905</v>
@@ -23926,30 +23992,27 @@
     </row>
     <row r="184" spans="1:8">
       <c r="A184" t="s">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="B184" t="s">
-        <v>989</v>
-      </c>
-      <c r="C184" t="s">
-        <v>523</v>
+        <v>984</v>
       </c>
       <c r="F184" t="s">
-        <v>990</v>
+        <v>361</v>
       </c>
       <c r="H184">
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:9">
+    <row r="185" spans="1:8">
       <c r="A185" t="s">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="B185" t="s">
-        <v>883</v>
+        <v>995</v>
       </c>
       <c r="E185" t="s">
-        <v>883</v>
+        <v>335</v>
       </c>
       <c r="F185" t="s">
         <v>905</v>
@@ -23957,19 +24020,16 @@
       <c r="H185">
         <v>1</v>
       </c>
-      <c r="I185">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="186" spans="1:8">
+    </row>
+    <row r="186" customFormat="1" spans="1:9">
       <c r="A186" t="s">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="B186" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
       <c r="E186" t="s">
-        <v>992</v>
+        <v>995</v>
       </c>
       <c r="F186" t="s">
         <v>905</v>
@@ -23977,16 +24037,19 @@
       <c r="H186">
         <v>1</v>
       </c>
-    </row>
-    <row r="187" spans="1:8">
+      <c r="I186">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="187" customFormat="1" spans="1:8">
       <c r="A187" t="s">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="B187" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
       <c r="E187" t="s">
-        <v>299</v>
+        <v>961</v>
       </c>
       <c r="F187" t="s">
         <v>905</v>
@@ -23997,13 +24060,16 @@
     </row>
     <row r="188" spans="1:8">
       <c r="A188" t="s">
-        <v>991</v>
+        <v>326</v>
       </c>
       <c r="B188" t="s">
-        <v>883</v>
+        <v>995</v>
+      </c>
+      <c r="E188" t="s">
+        <v>335</v>
       </c>
       <c r="F188" t="s">
-        <v>921</v>
+        <v>905</v>
       </c>
       <c r="H188">
         <v>1</v>
@@ -24011,13 +24077,13 @@
     </row>
     <row r="189" spans="1:8">
       <c r="A189" t="s">
-        <v>883</v>
+        <v>326</v>
       </c>
       <c r="B189" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="E189" t="s">
-        <v>302</v>
+        <v>996</v>
       </c>
       <c r="F189" t="s">
         <v>905</v>
@@ -24028,13 +24094,13 @@
     </row>
     <row r="190" spans="1:8">
       <c r="A190" t="s">
-        <v>883</v>
+        <v>326</v>
       </c>
       <c r="B190" t="s">
-        <v>993</v>
-      </c>
-      <c r="E190" s="9" t="s">
-        <v>994</v>
+        <v>995</v>
+      </c>
+      <c r="E190" t="s">
+        <v>961</v>
       </c>
       <c r="F190" t="s">
         <v>905</v>
@@ -24045,30 +24111,30 @@
     </row>
     <row r="191" spans="1:8">
       <c r="A191" t="s">
+        <v>290</v>
+      </c>
+      <c r="B191" t="s">
+        <v>997</v>
+      </c>
+      <c r="C191" t="s">
+        <v>523</v>
+      </c>
+      <c r="F191" t="s">
+        <v>998</v>
+      </c>
+      <c r="H191">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9">
+      <c r="A192" t="s">
+        <v>290</v>
+      </c>
+      <c r="B192" t="s">
         <v>883</v>
       </c>
-      <c r="B191" t="s">
-        <v>993</v>
-      </c>
-      <c r="E191" t="s">
-        <v>899</v>
-      </c>
-      <c r="F191" t="s">
-        <v>905</v>
-      </c>
-      <c r="H191">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="192" customFormat="1" spans="1:8">
-      <c r="A192" t="s">
+      <c r="E192" t="s">
         <v>883</v>
-      </c>
-      <c r="B192" t="s">
-        <v>995</v>
-      </c>
-      <c r="E192" t="s">
-        <v>302</v>
       </c>
       <c r="F192" t="s">
         <v>905</v>
@@ -24076,16 +24142,19 @@
       <c r="H192">
         <v>1</v>
       </c>
-    </row>
-    <row r="193" customFormat="1" spans="1:8">
+      <c r="I192">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8">
       <c r="A193" t="s">
-        <v>883</v>
+        <v>290</v>
       </c>
       <c r="B193" t="s">
-        <v>995</v>
-      </c>
-      <c r="E193" s="9" t="s">
-        <v>996</v>
+        <v>999</v>
+      </c>
+      <c r="E193" t="s">
+        <v>1000</v>
       </c>
       <c r="F193" t="s">
         <v>905</v>
@@ -24094,15 +24163,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" customFormat="1" spans="1:8">
+    <row r="194" spans="1:8">
       <c r="A194" t="s">
-        <v>883</v>
+        <v>290</v>
       </c>
       <c r="B194" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="E194" t="s">
-        <v>898</v>
+        <v>299</v>
       </c>
       <c r="F194" t="s">
         <v>905</v>
@@ -24113,16 +24182,13 @@
     </row>
     <row r="195" spans="1:8">
       <c r="A195" t="s">
-        <v>9</v>
+        <v>999</v>
       </c>
       <c r="B195" t="s">
-        <v>809</v>
-      </c>
-      <c r="C195" t="s">
-        <v>842</v>
+        <v>883</v>
       </c>
       <c r="F195" t="s">
-        <v>997</v>
+        <v>928</v>
       </c>
       <c r="H195">
         <v>1</v>
@@ -24130,39 +24196,413 @@
     </row>
     <row r="196" spans="1:8">
       <c r="A196" t="s">
+        <v>883</v>
+      </c>
+      <c r="B196" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E196" t="s">
+        <v>302</v>
+      </c>
+      <c r="F196" t="s">
+        <v>905</v>
+      </c>
+      <c r="H196">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8">
+      <c r="A197" t="s">
+        <v>883</v>
+      </c>
+      <c r="B197" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E197" s="9" t="s">
+        <v>1002</v>
+      </c>
+      <c r="F197" t="s">
+        <v>905</v>
+      </c>
+      <c r="H197">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8">
+      <c r="A198" t="s">
+        <v>883</v>
+      </c>
+      <c r="B198" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E198" t="s">
+        <v>899</v>
+      </c>
+      <c r="F198" t="s">
+        <v>905</v>
+      </c>
+      <c r="H198">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="199" customFormat="1" spans="1:8">
+      <c r="A199" t="s">
+        <v>883</v>
+      </c>
+      <c r="B199" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E199" t="s">
+        <v>302</v>
+      </c>
+      <c r="F199" t="s">
+        <v>905</v>
+      </c>
+      <c r="H199">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200" customFormat="1" spans="1:8">
+      <c r="A200" t="s">
+        <v>883</v>
+      </c>
+      <c r="B200" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E200" s="9" t="s">
+        <v>1004</v>
+      </c>
+      <c r="F200" t="s">
+        <v>905</v>
+      </c>
+      <c r="H200">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" customFormat="1" spans="1:8">
+      <c r="A201" t="s">
+        <v>883</v>
+      </c>
+      <c r="B201" t="s">
+        <v>1003</v>
+      </c>
+      <c r="E201" t="s">
+        <v>898</v>
+      </c>
+      <c r="F201" t="s">
+        <v>905</v>
+      </c>
+      <c r="H201">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8">
+      <c r="A202" t="s">
+        <v>9</v>
+      </c>
+      <c r="B202" t="s">
         <v>809</v>
       </c>
-      <c r="B196" t="s">
-        <v>998</v>
-      </c>
-      <c r="F196" t="s">
-        <v>998</v>
-      </c>
-      <c r="H196">
+      <c r="C202" t="s">
+        <v>842</v>
+      </c>
+      <c r="F202" t="s">
+        <v>1005</v>
+      </c>
+      <c r="H202">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8">
+      <c r="A203" t="s">
+        <v>809</v>
+      </c>
+      <c r="B203" t="s">
+        <v>1006</v>
+      </c>
+      <c r="F203" t="s">
+        <v>1006</v>
+      </c>
+      <c r="H203">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8">
+      <c r="A204" t="s">
+        <v>192</v>
+      </c>
+      <c r="B204" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C204" t="s">
+        <v>523</v>
+      </c>
+      <c r="F204" t="s">
+        <v>1008</v>
+      </c>
+      <c r="H204">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" customFormat="1" spans="1:8">
+      <c r="A205" t="s">
+        <v>192</v>
+      </c>
+      <c r="B205" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C205" t="s">
+        <v>523</v>
+      </c>
+      <c r="F205" t="s">
+        <v>1008</v>
+      </c>
+      <c r="H205">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8">
+      <c r="A206" t="s">
+        <v>192</v>
+      </c>
+      <c r="B206" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C206" t="s">
+        <v>1011</v>
+      </c>
+      <c r="F206" t="s">
+        <v>1012</v>
+      </c>
+      <c r="H206">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8">
+      <c r="A207" t="s">
+        <v>910</v>
+      </c>
+      <c r="B207" t="s">
+        <v>9</v>
+      </c>
+      <c r="C207" t="s">
+        <v>486</v>
+      </c>
+      <c r="F207" t="s">
+        <v>905</v>
+      </c>
+      <c r="H207">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8">
+      <c r="A208" t="s">
+        <v>192</v>
+      </c>
+      <c r="B208" t="s">
+        <v>264</v>
+      </c>
+      <c r="E208" t="s">
+        <v>264</v>
+      </c>
+      <c r="F208" t="s">
+        <v>905</v>
+      </c>
+      <c r="H208">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8">
+      <c r="A209" t="s">
+        <v>192</v>
+      </c>
+      <c r="B209" t="s">
+        <v>264</v>
+      </c>
+      <c r="E209" t="s">
+        <v>1013</v>
+      </c>
+      <c r="F209" t="s">
+        <v>905</v>
+      </c>
+      <c r="H209">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8">
+      <c r="A210" t="s">
+        <v>192</v>
+      </c>
+      <c r="B210" t="s">
+        <v>264</v>
+      </c>
+      <c r="C210" t="s">
+        <v>1014</v>
+      </c>
+      <c r="F210" t="s">
+        <v>1015</v>
+      </c>
+      <c r="H210">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8">
+      <c r="A211" t="s">
+        <v>192</v>
+      </c>
+      <c r="B211" t="s">
+        <v>264</v>
+      </c>
+      <c r="E211" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F211" t="s">
+        <v>905</v>
+      </c>
+      <c r="H211">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8">
+      <c r="A212" t="s">
+        <v>188</v>
+      </c>
+      <c r="B212" t="s">
+        <v>205</v>
+      </c>
+      <c r="E212" t="s">
+        <v>205</v>
+      </c>
+      <c r="F212" t="s">
+        <v>905</v>
+      </c>
+      <c r="H212">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8">
+      <c r="A213" t="s">
+        <v>188</v>
+      </c>
+      <c r="B213" t="s">
+        <v>205</v>
+      </c>
+      <c r="C213" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F213" t="s">
+        <v>920</v>
+      </c>
+      <c r="H213">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8">
+      <c r="A214" t="s">
+        <v>188</v>
+      </c>
+      <c r="B214" t="s">
+        <v>205</v>
+      </c>
+      <c r="C214" t="s">
+        <v>523</v>
+      </c>
+      <c r="F214" t="s">
+        <v>1008</v>
+      </c>
+      <c r="H214">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8">
+      <c r="A215" t="s">
+        <v>188</v>
+      </c>
+      <c r="B215" t="s">
+        <v>205</v>
+      </c>
+      <c r="E215" t="s">
+        <v>278</v>
+      </c>
+      <c r="F215" t="s">
+        <v>905</v>
+      </c>
+      <c r="H215">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8">
+      <c r="A216" t="s">
+        <v>188</v>
+      </c>
+      <c r="B216" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E216" t="s">
+        <v>205</v>
+      </c>
+      <c r="F216" t="s">
+        <v>905</v>
+      </c>
+      <c r="H216">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8">
+      <c r="A217" t="s">
+        <v>188</v>
+      </c>
+      <c r="B217" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C217" t="s">
+        <v>523</v>
+      </c>
+      <c r="F217" t="s">
+        <v>1008</v>
+      </c>
+      <c r="H217">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8">
+      <c r="A218" t="s">
+        <v>188</v>
+      </c>
+      <c r="B218" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E218" t="s">
+        <v>278</v>
+      </c>
+      <c r="F218" t="s">
+        <v>905</v>
+      </c>
+      <c r="H218">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="7">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F20 F104 F140:F141">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8 F9 F27 F111 F139 F147:F148">
       <formula1>"按钮, 文本框, 勾选框, 单选按钮,空值,非必选按钮"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F21 F49 F105">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F12 F13 F14 F15 F16 F64 F146 F159 F207 F208 F209 F211 F212 F213 F215 F216 F218 F2:F7 F10:F11 F17:F26 F29:F31 F33:F34 F36:F55 F57:F62 F66:F68 F75:F89 F92:F94 F96:F110 F113:F138 F140:F144 F151:F152 F156:F157 F162:F167 F169:F183 F185:F190 F196:F201 F192:G195">
+      <formula1>"按钮, 文本框, 勾选框, 单选按钮,空值"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F28 F56 F112">
       <formula1>"按钮, 文本框, 勾选框, 单选按钮,空值,可变文本"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F25">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F32">
       <formula1>"按钮, 文本框, 勾选框, 单选按钮,空值,contentDescMatches"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F28 F138 F161 F177 F62:F67 F83:F84 F142:F143 F146:F148">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F35 F145 F168 F184 F69:F74 F90:F91 F149:F150 F153:F155">
       <formula1>"按钮, 文本框, 勾选框, 单选按钮,空值,持续到页面跳转,截图"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F56 F58">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F63 F65">
       <formula1>"按钮, 文本框, 勾选框, 单选按钮,空值,可变文本,切换网络"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F57 F131 F132 F133 F139 F152 F197 F198 F199 F200 F2:F19 F22:F24 F26:F27 F29:F48 F50:F55 F59:F61 F68:F82 F85:F87 F89:F103 F106:F130 F134:F137 F144:F145 F149:F150 F155:F160 F162:F176 F178:F183 F189:F194 F185:G188">
-      <formula1>"按钮, 文本框, 勾选框, 单选按钮,空值"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F88">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F95">
       <formula1>"按钮, 文本框, 勾选框, 单选按钮,空值,获取文本"</formula1>
     </dataValidation>
   </dataValidations>
